--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -182,22 +182,22 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>NC</t>
@@ -966,7 +966,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -984,7 +984,7 @@
         <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1029,7 +1029,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1047,7 +1047,7 @@
         <v>6</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1055,7 +1055,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>-1</v>
@@ -1073,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1118,7 +1118,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -1136,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1144,7 +1144,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1207,7 +1207,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1322,7 +1322,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -1340,7 +1340,7 @@
         <v>5</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1385,7 +1385,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1403,7 +1403,7 @@
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1429,7 +1429,7 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1492,7 +1492,7 @@
         <v>5</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1500,7 +1500,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>9</v>
@@ -1518,7 +1518,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1563,7 +1563,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1581,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1589,7 +1589,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>6</v>
@@ -1604,7 +1604,7 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1643,7 +1643,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>6</v>
@@ -1658,7 +1658,7 @@
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1666,7 +1666,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1729,7 +1729,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1755,7 +1755,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -1773,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1818,7 +1818,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1836,7 +1836,7 @@
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1844,7 +1844,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>8</v>
@@ -1862,7 +1862,7 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1907,7 +1907,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1925,7 +1925,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1933,7 +1933,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1951,7 +1951,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1996,7 +1996,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -2014,7 +2014,7 @@
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2022,7 +2022,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -2040,7 +2040,7 @@
         <v>-1</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2085,7 +2085,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2103,7 +2103,7 @@
         <v>-1</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2111,7 +2111,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -2129,7 +2129,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2174,7 +2174,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -2192,7 +2192,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2200,7 +2200,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -2218,7 +2218,7 @@
         <v>-1</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2263,7 +2263,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2281,7 +2281,7 @@
         <v>-1</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2289,7 +2289,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>-1</v>
@@ -2307,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2352,7 +2352,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2370,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2378,7 +2378,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2441,7 +2441,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2459,7 +2459,7 @@
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2467,7 +2467,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>7</v>
@@ -2485,7 +2485,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2530,7 +2530,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2548,7 +2548,7 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2556,7 +2556,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -2574,7 +2574,7 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2619,7 +2619,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2637,7 +2637,7 @@
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2645,7 +2645,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>7</v>
@@ -2663,7 +2663,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2708,7 +2708,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2726,7 +2726,7 @@
         <v>7</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2734,7 +2734,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -2752,7 +2752,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2797,7 +2797,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>6</v>
@@ -2815,7 +2815,7 @@
         <v>6</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2823,7 +2823,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2886,7 +2886,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2904,7 +2904,7 @@
         <v>5</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2912,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>8</v>
@@ -2930,7 +2930,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2975,7 +2975,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2993,7 +2993,7 @@
         <v>7</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3001,7 +3001,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -3019,7 +3019,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3064,7 +3064,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -3082,7 +3082,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3090,7 +3090,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -3108,7 +3108,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3153,7 +3153,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -3171,7 +3171,7 @@
         <v>10</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3179,7 +3179,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -3197,7 +3197,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3242,7 +3242,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -3260,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3268,7 +3268,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -3286,7 +3286,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3331,7 +3331,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3349,7 +3349,7 @@
         <v>5</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3357,7 +3357,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -3375,7 +3375,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3420,7 +3420,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -3438,7 +3438,7 @@
         <v>10</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3446,7 +3446,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C32">
         <v>-1</v>
@@ -3464,7 +3464,7 @@
         <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3509,7 +3509,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>-1</v>
@@ -3527,7 +3527,7 @@
         <v>6</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3535,7 +3535,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C33">
         <v>6</v>
@@ -3553,7 +3553,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3598,7 +3598,7 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>6</v>
@@ -3616,7 +3616,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3624,7 +3624,7 @@
         <v>43</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>9</v>
@@ -3642,7 +3642,7 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3687,7 +3687,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3705,7 +3705,7 @@
         <v>5</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3790,13 +3790,13 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J3">
         <v>100</v>
@@ -3819,13 +3819,13 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3857,27 +3857,30 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>29.03</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3886,27 +3889,30 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>25.81</v>
+      </c>
+      <c r="H6">
+        <v>6.5</v>
       </c>
       <c r="I6">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3915,30 +3921,30 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>64.52</v>
+        <v>83.87</v>
       </c>
       <c r="G7">
-        <v>29.03</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>6.45</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -3947,25 +3953,25 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>83.87</v>
+        <v>93.55</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>16.13</v>
+        <v>6.45</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3981,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4036,7 +4042,7 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -4056,7 +4062,7 @@
         <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -4064,42 +4070,42 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920041</v>
+        <v>20330051920071</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920041</v>
+        <v>20330051920071</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4116,10 +4122,10 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4136,90 +4142,90 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4236,10 +4242,10 @@
         <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4256,104 +4262,104 @@
         <v>121</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E17" t="s">
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920073</v>
+        <v>20330051920359</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -4364,19 +4370,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920073</v>
+        <v>20330051920359</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>54</v>
@@ -4384,19 +4390,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920073</v>
+        <v>20330051920359</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
         <v>55</v>
@@ -4404,79 +4410,79 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920359</v>
+        <v>20330051920074</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920359</v>
+        <v>20330051920074</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
         <v>54</v>
@@ -4484,19 +4490,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920359</v>
+        <v>20330051920074</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
         <v>55</v>
@@ -4504,76 +4510,76 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920359</v>
+        <v>20330051920075</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920359</v>
+        <v>20330051920075</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920074</v>
+        <v>20330051920075</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920074</v>
+        <v>19330051920051</v>
       </c>
       <c r="B30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -4584,79 +4590,79 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920074</v>
+        <v>19330051920051</v>
       </c>
       <c r="B31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F34" t="s">
         <v>57</v>
@@ -4664,259 +4670,259 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E35" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E36" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920075</v>
+        <v>20330051920081</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>19330051920051</v>
+        <v>20330051920081</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>19330051920051</v>
+        <v>20330051920081</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C42" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D43" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920077</v>
+        <v>20330051920082</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920077</v>
+        <v>20330051920084</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E45" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920077</v>
+        <v>20330051920084</v>
       </c>
       <c r="B46" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920077</v>
+        <v>20330051920084</v>
       </c>
       <c r="B47" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C47" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
         <v>56</v>
@@ -4924,36 +4930,36 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920077</v>
+        <v>20330051920084</v>
       </c>
       <c r="B48" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C48" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920080</v>
+        <v>20330051920087</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -4964,19 +4970,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920080</v>
+        <v>20330051920087</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C50" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E50" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
         <v>54</v>
@@ -4984,19 +4990,19 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920080</v>
+        <v>20330051920087</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
         <v>55</v>
@@ -5004,476 +5010,476 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920080</v>
+        <v>20330051920088</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920080</v>
+        <v>20330051920088</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920081</v>
+        <v>20330051920088</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E54" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920081</v>
+        <v>20330051920088</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E55" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920081</v>
+        <v>20330051920089</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D56" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F56" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920081</v>
+        <v>20330051920089</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C57" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D57" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F57" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920081</v>
+        <v>20330051920089</v>
       </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D58" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>20330051920082</v>
+        <v>20330051920089</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D59" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920082</v>
+        <v>20330051920090</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D60" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E60" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920082</v>
+        <v>20330051920090</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C61" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920082</v>
+        <v>20330051920090</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D62" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920082</v>
+        <v>20330051920091</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920084</v>
+        <v>20330051920091</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D64" t="s">
         <v>131</v>
       </c>
       <c r="E64" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920084</v>
+        <v>20330051920091</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D65" t="s">
         <v>131</v>
       </c>
       <c r="E65" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>20330051920084</v>
+        <v>20330051920092</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D66" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F66" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>20330051920084</v>
+        <v>20330051920092</v>
       </c>
       <c r="B67" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D67" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>20330051920084</v>
+        <v>20330051920092</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D68" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E68" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>20330051920084</v>
+        <v>20330051920093</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D69" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E69" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F69" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>20330051920087</v>
+        <v>20330051920093</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D70" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E70" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>20330051920087</v>
+        <v>20330051920093</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C71" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D71" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E71" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>20330051920087</v>
+        <v>20330051920059</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C72" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D72" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F72" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>20330051920087</v>
+        <v>20330051920059</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C73" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D73" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E73" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>20330051920087</v>
+        <v>20330051920059</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C74" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D74" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E74" t="s">
         <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>20330051920088</v>
+        <v>20330051920061</v>
       </c>
       <c r="B75" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D75" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E75" t="s">
         <v>7</v>
@@ -5484,19 +5490,19 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>20330051920088</v>
+        <v>20330051920061</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C76" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D76" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E76" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F76" t="s">
         <v>54</v>
@@ -5504,19 +5510,19 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>20330051920088</v>
+        <v>20330051920061</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D77" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E77" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F77" t="s">
         <v>55</v>
@@ -5524,196 +5530,196 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>20330051920088</v>
+        <v>20330051920062</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D78" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F78" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>20330051920088</v>
+        <v>20330051920062</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D79" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E79" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F79" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>20330051920088</v>
+        <v>20330051920062</v>
       </c>
       <c r="B80" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D80" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E80" t="s">
         <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>20330051920089</v>
+        <v>20330051920063</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C81" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D81" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E81" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F81" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>20330051920089</v>
+        <v>20330051920063</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E82" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>20330051920089</v>
+        <v>20330051920063</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E83" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F83" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84">
-        <v>20330051920089</v>
+        <v>20330051920064</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D84" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F84" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85">
-        <v>20330051920089</v>
+        <v>20330051920064</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86">
-        <v>20330051920089</v>
+        <v>20330051920064</v>
       </c>
       <c r="B86" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C86" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D86" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E86" t="s">
         <v>9</v>
       </c>
       <c r="F86" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87">
-        <v>20330051920090</v>
+        <v>20330051920065</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E87" t="s">
         <v>7</v>
@@ -5724,19 +5730,19 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88">
-        <v>20330051920090</v>
+        <v>20330051920065</v>
       </c>
       <c r="B88" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C88" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E88" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F88" t="s">
         <v>54</v>
@@ -5744,19 +5750,19 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89">
-        <v>20330051920090</v>
+        <v>20330051920065</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E89" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F89" t="s">
         <v>55</v>
@@ -5764,156 +5770,156 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90">
-        <v>20330051920090</v>
+        <v>20330051920066</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F90" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91">
-        <v>20330051920090</v>
+        <v>20330051920066</v>
       </c>
       <c r="B91" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C91" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D91" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92">
-        <v>20330051920091</v>
+        <v>20330051920066</v>
       </c>
       <c r="B92" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C92" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D92" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="E92" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F92" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93">
-        <v>20330051920091</v>
+        <v>20330051920068</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C93" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E93" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94">
-        <v>20330051920091</v>
+        <v>20330051920068</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C94" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95">
-        <v>20330051920091</v>
+        <v>20330051920068</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C95" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E95" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96">
-        <v>20330051920091</v>
+        <v>20330051920070</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C96" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D96" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E96" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F96" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97">
-        <v>20330051920092</v>
+        <v>20330051920070</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C97" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E97" t="s">
         <v>7</v>
@@ -5924,19 +5930,19 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98">
-        <v>20330051920092</v>
+        <v>20330051920070</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C98" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D98" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E98" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F98" t="s">
         <v>54</v>
@@ -5944,19 +5950,19 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99">
-        <v>20330051920092</v>
+        <v>20330051920070</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C99" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E99" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F99" t="s">
         <v>55</v>
@@ -5964,1262 +5970,122 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100">
-        <v>20330051920092</v>
+        <v>20330051920069</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C100" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E100" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F100" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101">
-        <v>20330051920092</v>
+        <v>20330051920069</v>
       </c>
       <c r="B101" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C101" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="D101" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F101" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102">
-        <v>20330051920093</v>
+        <v>20330051920069</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C102" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D102" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E102" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F102" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103">
-        <v>20330051920093</v>
+        <v>20330051920386</v>
       </c>
       <c r="B103" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C103" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E103" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F103" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104">
-        <v>20330051920093</v>
+        <v>20330051920386</v>
       </c>
       <c r="B104" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C104" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
       </c>
       <c r="F104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105">
-        <v>20330051920093</v>
+        <v>20330051920386</v>
       </c>
       <c r="B105" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C105" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D105" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E105" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F105" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>20330051920093</v>
-      </c>
-      <c r="B106" t="s">
-        <v>81</v>
-      </c>
-      <c r="C106" t="s">
-        <v>109</v>
-      </c>
-      <c r="D106" t="s">
-        <v>137</v>
-      </c>
-      <c r="E106" t="s">
-        <v>9</v>
-      </c>
-      <c r="F106" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>20330051920059</v>
-      </c>
-      <c r="B107" t="s">
-        <v>82</v>
-      </c>
-      <c r="C107" t="s">
-        <v>110</v>
-      </c>
-      <c r="D107" t="s">
-        <v>138</v>
-      </c>
-      <c r="E107" t="s">
-        <v>7</v>
-      </c>
-      <c r="F107" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>20330051920059</v>
-      </c>
-      <c r="B108" t="s">
-        <v>82</v>
-      </c>
-      <c r="C108" t="s">
-        <v>110</v>
-      </c>
-      <c r="D108" t="s">
-        <v>138</v>
-      </c>
-      <c r="E108" t="s">
-        <v>5</v>
-      </c>
-      <c r="F108" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>20330051920059</v>
-      </c>
-      <c r="B109" t="s">
-        <v>82</v>
-      </c>
-      <c r="C109" t="s">
-        <v>110</v>
-      </c>
-      <c r="D109" t="s">
-        <v>138</v>
-      </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>20330051920059</v>
-      </c>
-      <c r="B110" t="s">
-        <v>82</v>
-      </c>
-      <c r="C110" t="s">
-        <v>110</v>
-      </c>
-      <c r="D110" t="s">
-        <v>138</v>
-      </c>
-      <c r="E110" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>20330051920059</v>
-      </c>
-      <c r="B111" t="s">
-        <v>82</v>
-      </c>
-      <c r="C111" t="s">
-        <v>110</v>
-      </c>
-      <c r="D111" t="s">
-        <v>138</v>
-      </c>
-      <c r="E111" t="s">
-        <v>9</v>
-      </c>
-      <c r="F111" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>20330051920061</v>
-      </c>
-      <c r="B112" t="s">
-        <v>83</v>
-      </c>
-      <c r="C112" t="s">
-        <v>111</v>
-      </c>
-      <c r="D112" t="s">
-        <v>139</v>
-      </c>
-      <c r="E112" t="s">
-        <v>7</v>
-      </c>
-      <c r="F112" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>20330051920061</v>
-      </c>
-      <c r="B113" t="s">
-        <v>83</v>
-      </c>
-      <c r="C113" t="s">
-        <v>111</v>
-      </c>
-      <c r="D113" t="s">
-        <v>139</v>
-      </c>
-      <c r="E113" t="s">
-        <v>5</v>
-      </c>
-      <c r="F113" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>20330051920061</v>
-      </c>
-      <c r="B114" t="s">
-        <v>83</v>
-      </c>
-      <c r="C114" t="s">
-        <v>111</v>
-      </c>
-      <c r="D114" t="s">
-        <v>139</v>
-      </c>
-      <c r="E114" t="s">
-        <v>8</v>
-      </c>
-      <c r="F114" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>20330051920061</v>
-      </c>
-      <c r="B115" t="s">
-        <v>83</v>
-      </c>
-      <c r="C115" t="s">
-        <v>111</v>
-      </c>
-      <c r="D115" t="s">
-        <v>139</v>
-      </c>
-      <c r="E115" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>20330051920061</v>
-      </c>
-      <c r="B116" t="s">
-        <v>83</v>
-      </c>
-      <c r="C116" t="s">
-        <v>111</v>
-      </c>
-      <c r="D116" t="s">
-        <v>139</v>
-      </c>
-      <c r="E116" t="s">
-        <v>9</v>
-      </c>
-      <c r="F116" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>20330051920062</v>
-      </c>
-      <c r="B117" t="s">
-        <v>84</v>
-      </c>
-      <c r="C117" t="s">
-        <v>82</v>
-      </c>
-      <c r="D117" t="s">
-        <v>140</v>
-      </c>
-      <c r="E117" t="s">
-        <v>7</v>
-      </c>
-      <c r="F117" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>20330051920062</v>
-      </c>
-      <c r="B118" t="s">
-        <v>84</v>
-      </c>
-      <c r="C118" t="s">
-        <v>82</v>
-      </c>
-      <c r="D118" t="s">
-        <v>140</v>
-      </c>
-      <c r="E118" t="s">
-        <v>5</v>
-      </c>
-      <c r="F118" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>20330051920062</v>
-      </c>
-      <c r="B119" t="s">
-        <v>84</v>
-      </c>
-      <c r="C119" t="s">
-        <v>82</v>
-      </c>
-      <c r="D119" t="s">
-        <v>140</v>
-      </c>
-      <c r="E119" t="s">
-        <v>8</v>
-      </c>
-      <c r="F119" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>20330051920062</v>
-      </c>
-      <c r="B120" t="s">
-        <v>84</v>
-      </c>
-      <c r="C120" t="s">
-        <v>82</v>
-      </c>
-      <c r="D120" t="s">
-        <v>140</v>
-      </c>
-      <c r="E120" t="s">
-        <v>11</v>
-      </c>
-      <c r="F120" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>20330051920062</v>
-      </c>
-      <c r="B121" t="s">
-        <v>84</v>
-      </c>
-      <c r="C121" t="s">
-        <v>82</v>
-      </c>
-      <c r="D121" t="s">
-        <v>140</v>
-      </c>
-      <c r="E121" t="s">
-        <v>9</v>
-      </c>
-      <c r="F121" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>20330051920063</v>
-      </c>
-      <c r="B122" t="s">
-        <v>85</v>
-      </c>
-      <c r="C122" t="s">
-        <v>112</v>
-      </c>
-      <c r="D122" t="s">
-        <v>141</v>
-      </c>
-      <c r="E122" t="s">
-        <v>7</v>
-      </c>
-      <c r="F122" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>20330051920063</v>
-      </c>
-      <c r="B123" t="s">
-        <v>85</v>
-      </c>
-      <c r="C123" t="s">
-        <v>112</v>
-      </c>
-      <c r="D123" t="s">
-        <v>141</v>
-      </c>
-      <c r="E123" t="s">
-        <v>5</v>
-      </c>
-      <c r="F123" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>20330051920063</v>
-      </c>
-      <c r="B124" t="s">
-        <v>85</v>
-      </c>
-      <c r="C124" t="s">
-        <v>112</v>
-      </c>
-      <c r="D124" t="s">
-        <v>141</v>
-      </c>
-      <c r="E124" t="s">
-        <v>8</v>
-      </c>
-      <c r="F124" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>20330051920063</v>
-      </c>
-      <c r="B125" t="s">
-        <v>85</v>
-      </c>
-      <c r="C125" t="s">
-        <v>112</v>
-      </c>
-      <c r="D125" t="s">
-        <v>141</v>
-      </c>
-      <c r="E125" t="s">
-        <v>11</v>
-      </c>
-      <c r="F125" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>20330051920063</v>
-      </c>
-      <c r="B126" t="s">
-        <v>85</v>
-      </c>
-      <c r="C126" t="s">
-        <v>112</v>
-      </c>
-      <c r="D126" t="s">
-        <v>141</v>
-      </c>
-      <c r="E126" t="s">
-        <v>9</v>
-      </c>
-      <c r="F126" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>20330051920064</v>
-      </c>
-      <c r="B127" t="s">
-        <v>86</v>
-      </c>
-      <c r="C127" t="s">
-        <v>113</v>
-      </c>
-      <c r="D127" t="s">
-        <v>142</v>
-      </c>
-      <c r="E127" t="s">
-        <v>7</v>
-      </c>
-      <c r="F127" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>20330051920064</v>
-      </c>
-      <c r="B128" t="s">
-        <v>86</v>
-      </c>
-      <c r="C128" t="s">
-        <v>113</v>
-      </c>
-      <c r="D128" t="s">
-        <v>142</v>
-      </c>
-      <c r="E128" t="s">
-        <v>5</v>
-      </c>
-      <c r="F128" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>20330051920064</v>
-      </c>
-      <c r="B129" t="s">
-        <v>86</v>
-      </c>
-      <c r="C129" t="s">
-        <v>113</v>
-      </c>
-      <c r="D129" t="s">
-        <v>142</v>
-      </c>
-      <c r="E129" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>20330051920064</v>
-      </c>
-      <c r="B130" t="s">
-        <v>86</v>
-      </c>
-      <c r="C130" t="s">
-        <v>113</v>
-      </c>
-      <c r="D130" t="s">
-        <v>142</v>
-      </c>
-      <c r="E130" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>20330051920064</v>
-      </c>
-      <c r="B131" t="s">
-        <v>86</v>
-      </c>
-      <c r="C131" t="s">
-        <v>113</v>
-      </c>
-      <c r="D131" t="s">
-        <v>142</v>
-      </c>
-      <c r="E131" t="s">
-        <v>9</v>
-      </c>
-      <c r="F131" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>20330051920065</v>
-      </c>
-      <c r="B132" t="s">
-        <v>87</v>
-      </c>
-      <c r="C132" t="s">
-        <v>114</v>
-      </c>
-      <c r="D132" t="s">
-        <v>143</v>
-      </c>
-      <c r="E132" t="s">
-        <v>7</v>
-      </c>
-      <c r="F132" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>20330051920065</v>
-      </c>
-      <c r="B133" t="s">
-        <v>87</v>
-      </c>
-      <c r="C133" t="s">
-        <v>114</v>
-      </c>
-      <c r="D133" t="s">
-        <v>143</v>
-      </c>
-      <c r="E133" t="s">
-        <v>5</v>
-      </c>
-      <c r="F133" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>20330051920065</v>
-      </c>
-      <c r="B134" t="s">
-        <v>87</v>
-      </c>
-      <c r="C134" t="s">
-        <v>114</v>
-      </c>
-      <c r="D134" t="s">
-        <v>143</v>
-      </c>
-      <c r="E134" t="s">
-        <v>8</v>
-      </c>
-      <c r="F134" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>20330051920065</v>
-      </c>
-      <c r="B135" t="s">
-        <v>87</v>
-      </c>
-      <c r="C135" t="s">
-        <v>114</v>
-      </c>
-      <c r="D135" t="s">
-        <v>143</v>
-      </c>
-      <c r="E135" t="s">
-        <v>11</v>
-      </c>
-      <c r="F135" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>20330051920065</v>
-      </c>
-      <c r="B136" t="s">
-        <v>87</v>
-      </c>
-      <c r="C136" t="s">
-        <v>114</v>
-      </c>
-      <c r="D136" t="s">
-        <v>143</v>
-      </c>
-      <c r="E136" t="s">
-        <v>9</v>
-      </c>
-      <c r="F136" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>20330051920066</v>
-      </c>
-      <c r="B137" t="s">
-        <v>88</v>
-      </c>
-      <c r="C137" t="s">
-        <v>115</v>
-      </c>
-      <c r="D137" t="s">
-        <v>144</v>
-      </c>
-      <c r="E137" t="s">
-        <v>7</v>
-      </c>
-      <c r="F137" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>20330051920066</v>
-      </c>
-      <c r="B138" t="s">
-        <v>88</v>
-      </c>
-      <c r="C138" t="s">
-        <v>115</v>
-      </c>
-      <c r="D138" t="s">
-        <v>144</v>
-      </c>
-      <c r="E138" t="s">
-        <v>5</v>
-      </c>
-      <c r="F138" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>20330051920066</v>
-      </c>
-      <c r="B139" t="s">
-        <v>88</v>
-      </c>
-      <c r="C139" t="s">
-        <v>115</v>
-      </c>
-      <c r="D139" t="s">
-        <v>144</v>
-      </c>
-      <c r="E139" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>20330051920066</v>
-      </c>
-      <c r="B140" t="s">
-        <v>88</v>
-      </c>
-      <c r="C140" t="s">
-        <v>115</v>
-      </c>
-      <c r="D140" t="s">
-        <v>144</v>
-      </c>
-      <c r="E140" t="s">
-        <v>11</v>
-      </c>
-      <c r="F140" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>20330051920066</v>
-      </c>
-      <c r="B141" t="s">
-        <v>88</v>
-      </c>
-      <c r="C141" t="s">
-        <v>115</v>
-      </c>
-      <c r="D141" t="s">
-        <v>144</v>
-      </c>
-      <c r="E141" t="s">
-        <v>9</v>
-      </c>
-      <c r="F141" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
-      <c r="A142">
-        <v>20330051920068</v>
-      </c>
-      <c r="B142" t="s">
-        <v>89</v>
-      </c>
-      <c r="C142" t="s">
-        <v>73</v>
-      </c>
-      <c r="D142" t="s">
-        <v>145</v>
-      </c>
-      <c r="E142" t="s">
-        <v>7</v>
-      </c>
-      <c r="F142" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
-      <c r="A143">
-        <v>20330051920068</v>
-      </c>
-      <c r="B143" t="s">
-        <v>89</v>
-      </c>
-      <c r="C143" t="s">
-        <v>73</v>
-      </c>
-      <c r="D143" t="s">
-        <v>145</v>
-      </c>
-      <c r="E143" t="s">
-        <v>5</v>
-      </c>
-      <c r="F143" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="A144">
-        <v>20330051920068</v>
-      </c>
-      <c r="B144" t="s">
-        <v>89</v>
-      </c>
-      <c r="C144" t="s">
-        <v>73</v>
-      </c>
-      <c r="D144" t="s">
-        <v>145</v>
-      </c>
-      <c r="E144" t="s">
-        <v>8</v>
-      </c>
-      <c r="F144" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
-      <c r="A145">
-        <v>20330051920068</v>
-      </c>
-      <c r="B145" t="s">
-        <v>89</v>
-      </c>
-      <c r="C145" t="s">
-        <v>73</v>
-      </c>
-      <c r="D145" t="s">
-        <v>145</v>
-      </c>
-      <c r="E145" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="A146">
-        <v>20330051920068</v>
-      </c>
-      <c r="B146" t="s">
-        <v>89</v>
-      </c>
-      <c r="C146" t="s">
-        <v>73</v>
-      </c>
-      <c r="D146" t="s">
-        <v>145</v>
-      </c>
-      <c r="E146" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
-      <c r="A147">
-        <v>20330051920070</v>
-      </c>
-      <c r="B147" t="s">
-        <v>89</v>
-      </c>
-      <c r="C147" t="s">
-        <v>116</v>
-      </c>
-      <c r="D147" t="s">
-        <v>146</v>
-      </c>
-      <c r="E147" t="s">
-        <v>6</v>
-      </c>
-      <c r="F147" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148">
-        <v>20330051920070</v>
-      </c>
-      <c r="B148" t="s">
-        <v>89</v>
-      </c>
-      <c r="C148" t="s">
-        <v>116</v>
-      </c>
-      <c r="D148" t="s">
-        <v>146</v>
-      </c>
-      <c r="E148" t="s">
-        <v>7</v>
-      </c>
-      <c r="F148" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149">
-        <v>20330051920070</v>
-      </c>
-      <c r="B149" t="s">
-        <v>89</v>
-      </c>
-      <c r="C149" t="s">
-        <v>116</v>
-      </c>
-      <c r="D149" t="s">
-        <v>146</v>
-      </c>
-      <c r="E149" t="s">
-        <v>5</v>
-      </c>
-      <c r="F149" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150">
-        <v>20330051920070</v>
-      </c>
-      <c r="B150" t="s">
-        <v>89</v>
-      </c>
-      <c r="C150" t="s">
-        <v>116</v>
-      </c>
-      <c r="D150" t="s">
-        <v>146</v>
-      </c>
-      <c r="E150" t="s">
-        <v>8</v>
-      </c>
-      <c r="F150" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151">
-        <v>20330051920070</v>
-      </c>
-      <c r="B151" t="s">
-        <v>89</v>
-      </c>
-      <c r="C151" t="s">
-        <v>116</v>
-      </c>
-      <c r="D151" t="s">
-        <v>146</v>
-      </c>
-      <c r="E151" t="s">
-        <v>11</v>
-      </c>
-      <c r="F151" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152">
-        <v>20330051920070</v>
-      </c>
-      <c r="B152" t="s">
-        <v>89</v>
-      </c>
-      <c r="C152" t="s">
-        <v>116</v>
-      </c>
-      <c r="D152" t="s">
-        <v>146</v>
-      </c>
-      <c r="E152" t="s">
-        <v>9</v>
-      </c>
-      <c r="F152" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153">
-        <v>20330051920069</v>
-      </c>
-      <c r="B153" t="s">
-        <v>90</v>
-      </c>
-      <c r="C153" t="s">
-        <v>117</v>
-      </c>
-      <c r="D153" t="s">
-        <v>147</v>
-      </c>
-      <c r="E153" t="s">
-        <v>7</v>
-      </c>
-      <c r="F153" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154">
-        <v>20330051920069</v>
-      </c>
-      <c r="B154" t="s">
-        <v>90</v>
-      </c>
-      <c r="C154" t="s">
-        <v>117</v>
-      </c>
-      <c r="D154" t="s">
-        <v>147</v>
-      </c>
-      <c r="E154" t="s">
-        <v>5</v>
-      </c>
-      <c r="F154" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155">
-        <v>20330051920069</v>
-      </c>
-      <c r="B155" t="s">
-        <v>90</v>
-      </c>
-      <c r="C155" t="s">
-        <v>117</v>
-      </c>
-      <c r="D155" t="s">
-        <v>147</v>
-      </c>
-      <c r="E155" t="s">
-        <v>8</v>
-      </c>
-      <c r="F155" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156">
-        <v>20330051920069</v>
-      </c>
-      <c r="B156" t="s">
-        <v>90</v>
-      </c>
-      <c r="C156" t="s">
-        <v>117</v>
-      </c>
-      <c r="D156" t="s">
-        <v>147</v>
-      </c>
-      <c r="E156" t="s">
-        <v>11</v>
-      </c>
-      <c r="F156" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157">
-        <v>20330051920069</v>
-      </c>
-      <c r="B157" t="s">
-        <v>90</v>
-      </c>
-      <c r="C157" t="s">
-        <v>117</v>
-      </c>
-      <c r="D157" t="s">
-        <v>147</v>
-      </c>
-      <c r="E157" t="s">
-        <v>9</v>
-      </c>
-      <c r="F157" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158">
-        <v>20330051920386</v>
-      </c>
-      <c r="B158" t="s">
-        <v>91</v>
-      </c>
-      <c r="C158" t="s">
-        <v>118</v>
-      </c>
-      <c r="D158" t="s">
-        <v>148</v>
-      </c>
-      <c r="E158" t="s">
-        <v>7</v>
-      </c>
-      <c r="F158" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159">
-        <v>20330051920386</v>
-      </c>
-      <c r="B159" t="s">
-        <v>91</v>
-      </c>
-      <c r="C159" t="s">
-        <v>118</v>
-      </c>
-      <c r="D159" t="s">
-        <v>148</v>
-      </c>
-      <c r="E159" t="s">
-        <v>5</v>
-      </c>
-      <c r="F159" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160">
-        <v>20330051920386</v>
-      </c>
-      <c r="B160" t="s">
-        <v>91</v>
-      </c>
-      <c r="C160" t="s">
-        <v>118</v>
-      </c>
-      <c r="D160" t="s">
-        <v>148</v>
-      </c>
-      <c r="E160" t="s">
-        <v>8</v>
-      </c>
-      <c r="F160" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161">
-        <v>20330051920386</v>
-      </c>
-      <c r="B161" t="s">
-        <v>91</v>
-      </c>
-      <c r="C161" t="s">
-        <v>118</v>
-      </c>
-      <c r="D161" t="s">
-        <v>148</v>
-      </c>
-      <c r="E161" t="s">
-        <v>11</v>
-      </c>
-      <c r="F161" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162">
-        <v>20330051920386</v>
-      </c>
-      <c r="B162" t="s">
-        <v>91</v>
-      </c>
-      <c r="C162" t="s">
-        <v>118</v>
-      </c>
-      <c r="D162" t="s">
-        <v>148</v>
-      </c>
-      <c r="E162" t="s">
-        <v>9</v>
-      </c>
-      <c r="F162" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -7255,16 +6121,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -7272,189 +6138,189 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920074</v>
+        <v>20330051920071</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920084</v>
+        <v>20330051920073</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920088</v>
+        <v>20330051920077</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920089</v>
+        <v>20330051920084</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920070</v>
+        <v>20330051920088</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920041</v>
+        <v>20330051920089</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920073</v>
+        <v>20330051920070</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920359</v>
+        <v>20330051920041</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920075</v>
+        <v>20330051920359</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920077</v>
+        <v>20330051920075</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7471,7 +6337,7 @@
         <v>128</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7488,7 +6354,7 @@
         <v>129</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7505,7 +6371,7 @@
         <v>130</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7522,7 +6388,7 @@
         <v>132</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7539,7 +6405,7 @@
         <v>135</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7556,7 +6422,7 @@
         <v>131</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7573,7 +6439,7 @@
         <v>136</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7590,7 +6456,7 @@
         <v>137</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -7607,7 +6473,7 @@
         <v>138</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -7624,7 +6490,7 @@
         <v>139</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -7641,7 +6507,7 @@
         <v>140</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -7658,7 +6524,7 @@
         <v>141</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -7675,7 +6541,7 @@
         <v>142</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7692,7 +6558,7 @@
         <v>143</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -7709,7 +6575,7 @@
         <v>144</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -7726,7 +6592,7 @@
         <v>145</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7743,7 +6609,7 @@
         <v>147</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -7760,7 +6626,7 @@
         <v>148</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -7777,7 +6643,7 @@
         <v>126</v>
       </c>
       <c r="E32">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,15 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -212,259 +212,259 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
     <t>AVENDAÑO</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
     <t>BAROJAS</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
     <t>AXEL JESUS</t>
   </si>
   <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
     <t>KARLA JOVANA</t>
   </si>
   <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
     <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
 </sst>
 </file>
@@ -972,13 +972,13 @@
         <v>9</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -1035,13 +1035,13 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>6</v>
@@ -1156,7 +1156,7 @@
         <v>-1</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -1219,7 +1219,7 @@
         <v>-1</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1328,13 +1328,13 @@
         <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1391,13 +1391,13 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>5</v>
@@ -1509,7 +1509,7 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F10">
         <v>-1</v>
@@ -1572,7 +1572,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <v>-1</v>
@@ -1598,7 +1598,7 @@
         <v>-1</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -1652,7 +1652,7 @@
         <v>-1</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>10</v>
@@ -1767,7 +1767,7 @@
         <v>-1</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -1830,7 +1830,7 @@
         <v>-1</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>5</v>
@@ -1853,10 +1853,10 @@
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1916,10 +1916,10 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1942,10 +1942,10 @@
         <v>-1</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>7</v>
@@ -2005,10 +2005,10 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>7</v>
@@ -2034,7 +2034,7 @@
         <v>-1</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -2097,7 +2097,7 @@
         <v>-1</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>-1</v>
@@ -2123,7 +2123,7 @@
         <v>-1</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>8</v>
@@ -2186,7 +2186,7 @@
         <v>-1</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB17">
         <v>8</v>
@@ -2212,7 +2212,7 @@
         <v>-1</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -2275,7 +2275,7 @@
         <v>-1</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB18">
         <v>-1</v>
@@ -2384,13 +2384,13 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G20">
         <v>10</v>
@@ -2447,13 +2447,13 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>10</v>
@@ -2476,10 +2476,10 @@
         <v>-1</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -2539,10 +2539,10 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB21">
         <v>7</v>
@@ -2654,10 +2654,10 @@
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G23">
         <v>7</v>
@@ -2717,10 +2717,10 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>7</v>
@@ -2835,7 +2835,7 @@
         <v>-1</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -2898,7 +2898,7 @@
         <v>-1</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>5</v>
@@ -2921,10 +2921,10 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G26">
         <v>7</v>
@@ -2984,10 +2984,10 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>7</v>
@@ -3010,10 +3010,10 @@
         <v>-1</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G27">
         <v>10</v>
@@ -3073,10 +3073,10 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB27">
         <v>10</v>
@@ -3099,10 +3099,10 @@
         <v>-1</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G28">
         <v>10</v>
@@ -3162,10 +3162,10 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>10</v>
@@ -3191,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>6</v>
@@ -3254,7 +3254,7 @@
         <v>-1</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>6</v>
@@ -3280,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3343,7 +3343,7 @@
         <v>-1</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB30">
         <v>5</v>
@@ -3369,7 +3369,7 @@
         <v>-1</v>
       </c>
       <c r="F31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>10</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>10</v>
@@ -3544,7 +3544,7 @@
         <v>-1</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>-1</v>
@@ -3607,7 +3607,7 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>-1</v>
@@ -3633,7 +3633,7 @@
         <v>-1</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -3696,7 +3696,7 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA34">
         <v>-1</v>
@@ -3770,22 +3770,25 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.68</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>7.3</v>
+      </c>
       <c r="I2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3799,27 +3802,30 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3.33</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
       <c r="I3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3828,27 +3834,30 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>29.03</v>
+      </c>
+      <c r="H4">
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3860,27 +3869,27 @@
         <v>20</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>64.52</v>
       </c>
       <c r="G5">
-        <v>29.03</v>
+        <v>25.81</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>6.45</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3892,22 +3901,22 @@
         <v>20</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>64.52</v>
       </c>
       <c r="G6">
-        <v>25.81</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>9.68</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3981,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4010,62 +4019,62 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920041</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920041</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920041</v>
+        <v>20330051920071</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4073,79 +4082,79 @@
         <v>20330051920071</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4153,19 +4162,19 @@
         <v>20330051920072</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4173,19 +4182,19 @@
         <v>20330051920072</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4193,253 +4202,253 @@
         <v>20330051920072</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B12" t="s">
         <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B13" t="s">
         <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B14" t="s">
         <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B15" t="s">
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B16" t="s">
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B17" t="s">
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B18" t="s">
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920359</v>
+        <v>20330051920074</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920359</v>
+        <v>20330051920075</v>
       </c>
       <c r="B20" t="s">
         <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920359</v>
+        <v>20330051920075</v>
       </c>
       <c r="B21" t="s">
         <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920074</v>
+        <v>19330051920051</v>
       </c>
       <c r="B22" t="s">
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -4450,76 +4459,76 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -4530,16 +4539,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -4550,27 +4559,27 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920075</v>
+        <v>20330051920081</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
         <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B30" t="s">
         <v>71</v>
@@ -4579,7 +4588,7 @@
         <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -4590,27 +4599,27 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920051</v>
+        <v>20330051920084</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920077</v>
+        <v>20330051920084</v>
       </c>
       <c r="B32" t="s">
         <v>72</v>
@@ -4619,18 +4628,18 @@
         <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920077</v>
+        <v>20330051920084</v>
       </c>
       <c r="B33" t="s">
         <v>72</v>
@@ -4639,67 +4648,67 @@
         <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920077</v>
+        <v>20330051920087</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920077</v>
+        <v>20330051920087</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920080</v>
+        <v>20330051920088</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -4710,16 +4719,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920080</v>
+        <v>20330051920088</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4730,19 +4739,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920080</v>
+        <v>20330051920088</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" t="s">
         <v>55</v>
@@ -4750,436 +4759,436 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920081</v>
+        <v>20330051920089</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920081</v>
+        <v>20330051920089</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920081</v>
+        <v>20330051920089</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920082</v>
+        <v>20330051920089</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C42" t="s">
         <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920082</v>
+        <v>20330051920091</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920082</v>
+        <v>20330051920092</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920084</v>
+        <v>20330051920092</v>
       </c>
       <c r="B45" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D45" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920084</v>
+        <v>20330051920092</v>
       </c>
       <c r="B46" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D46" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920084</v>
+        <v>20330051920093</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F47" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920084</v>
+        <v>20330051920059</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D48" t="s">
         <v>131</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920087</v>
+        <v>20330051920059</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C49" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E49" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920087</v>
+        <v>20330051920059</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C50" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C51" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D51" t="s">
         <v>132</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920088</v>
+        <v>20330051920061</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D52" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920088</v>
+        <v>20330051920062</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C53" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
         <v>133</v>
       </c>
       <c r="E53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920088</v>
+        <v>20330051920063</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C54" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920088</v>
+        <v>20330051920064</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C55" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D55" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920089</v>
+        <v>20330051920065</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D56" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E56" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920089</v>
+        <v>20330051920065</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D57" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E57" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920089</v>
+        <v>20330051920066</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D58" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>20330051920089</v>
+        <v>20330051920066</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D59" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920090</v>
+        <v>20330051920068</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E60" t="s">
         <v>7</v>
@@ -5190,16 +5199,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920090</v>
+        <v>20330051920068</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5210,36 +5219,36 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920090</v>
+        <v>20330051920070</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F62" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920091</v>
+        <v>20330051920070</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E63" t="s">
         <v>7</v>
@@ -5250,16 +5259,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920091</v>
+        <v>20330051920070</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -5270,36 +5279,36 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920091</v>
+        <v>20330051920070</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>20330051920092</v>
+        <v>20330051920069</v>
       </c>
       <c r="B66" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C66" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D66" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E66" t="s">
         <v>7</v>
@@ -5310,782 +5319,62 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>20330051920092</v>
+        <v>20330051920069</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C67" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D67" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F67" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>20330051920092</v>
+        <v>20330051920386</v>
       </c>
       <c r="B68" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C68" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F68" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>20330051920093</v>
+        <v>20330051920386</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E69" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920093</v>
-      </c>
-      <c r="B70" t="s">
-        <v>81</v>
-      </c>
-      <c r="C70" t="s">
-        <v>109</v>
-      </c>
-      <c r="D70" t="s">
-        <v>137</v>
-      </c>
-      <c r="E70" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920093</v>
-      </c>
-      <c r="B71" t="s">
-        <v>81</v>
-      </c>
-      <c r="C71" t="s">
-        <v>109</v>
-      </c>
-      <c r="D71" t="s">
-        <v>137</v>
-      </c>
-      <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920059</v>
-      </c>
-      <c r="B72" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" t="s">
-        <v>110</v>
-      </c>
-      <c r="D72" t="s">
-        <v>138</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920059</v>
-      </c>
-      <c r="B73" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" t="s">
-        <v>110</v>
-      </c>
-      <c r="D73" t="s">
-        <v>138</v>
-      </c>
-      <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920059</v>
-      </c>
-      <c r="B74" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" t="s">
-        <v>110</v>
-      </c>
-      <c r="D74" t="s">
-        <v>138</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920061</v>
-      </c>
-      <c r="B75" t="s">
-        <v>83</v>
-      </c>
-      <c r="C75" t="s">
-        <v>111</v>
-      </c>
-      <c r="D75" t="s">
-        <v>139</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920061</v>
-      </c>
-      <c r="B76" t="s">
-        <v>83</v>
-      </c>
-      <c r="C76" t="s">
-        <v>111</v>
-      </c>
-      <c r="D76" t="s">
-        <v>139</v>
-      </c>
-      <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920061</v>
-      </c>
-      <c r="B77" t="s">
-        <v>83</v>
-      </c>
-      <c r="C77" t="s">
-        <v>111</v>
-      </c>
-      <c r="D77" t="s">
-        <v>139</v>
-      </c>
-      <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920062</v>
-      </c>
-      <c r="B78" t="s">
-        <v>84</v>
-      </c>
-      <c r="C78" t="s">
-        <v>82</v>
-      </c>
-      <c r="D78" t="s">
-        <v>140</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920062</v>
-      </c>
-      <c r="B79" t="s">
-        <v>84</v>
-      </c>
-      <c r="C79" t="s">
-        <v>82</v>
-      </c>
-      <c r="D79" t="s">
-        <v>140</v>
-      </c>
-      <c r="E79" t="s">
-        <v>8</v>
-      </c>
-      <c r="F79" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920062</v>
-      </c>
-      <c r="B80" t="s">
-        <v>84</v>
-      </c>
-      <c r="C80" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" t="s">
-        <v>140</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920063</v>
-      </c>
-      <c r="B81" t="s">
-        <v>85</v>
-      </c>
-      <c r="C81" t="s">
-        <v>112</v>
-      </c>
-      <c r="D81" t="s">
-        <v>141</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920063</v>
-      </c>
-      <c r="B82" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" t="s">
-        <v>112</v>
-      </c>
-      <c r="D82" t="s">
-        <v>141</v>
-      </c>
-      <c r="E82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920063</v>
-      </c>
-      <c r="B83" t="s">
-        <v>85</v>
-      </c>
-      <c r="C83" t="s">
-        <v>112</v>
-      </c>
-      <c r="D83" t="s">
-        <v>141</v>
-      </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920064</v>
-      </c>
-      <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84" t="s">
-        <v>113</v>
-      </c>
-      <c r="D84" t="s">
-        <v>142</v>
-      </c>
-      <c r="E84" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920064</v>
-      </c>
-      <c r="B85" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>113</v>
-      </c>
-      <c r="D85" t="s">
-        <v>142</v>
-      </c>
-      <c r="E85" t="s">
-        <v>8</v>
-      </c>
-      <c r="F85" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920064</v>
-      </c>
-      <c r="B86" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D86" t="s">
-        <v>142</v>
-      </c>
-      <c r="E86" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920065</v>
-      </c>
-      <c r="B87" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" t="s">
-        <v>114</v>
-      </c>
-      <c r="D87" t="s">
-        <v>143</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920065</v>
-      </c>
-      <c r="B88" t="s">
-        <v>87</v>
-      </c>
-      <c r="C88" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" t="s">
-        <v>143</v>
-      </c>
-      <c r="E88" t="s">
-        <v>8</v>
-      </c>
-      <c r="F88" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920065</v>
-      </c>
-      <c r="B89" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" t="s">
-        <v>114</v>
-      </c>
-      <c r="D89" t="s">
-        <v>143</v>
-      </c>
-      <c r="E89" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>20330051920066</v>
-      </c>
-      <c r="B90" t="s">
-        <v>88</v>
-      </c>
-      <c r="C90" t="s">
-        <v>115</v>
-      </c>
-      <c r="D90" t="s">
-        <v>144</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>20330051920066</v>
-      </c>
-      <c r="B91" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" t="s">
-        <v>115</v>
-      </c>
-      <c r="D91" t="s">
-        <v>144</v>
-      </c>
-      <c r="E91" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>20330051920066</v>
-      </c>
-      <c r="B92" t="s">
-        <v>88</v>
-      </c>
-      <c r="C92" t="s">
-        <v>115</v>
-      </c>
-      <c r="D92" t="s">
-        <v>144</v>
-      </c>
-      <c r="E92" t="s">
-        <v>9</v>
-      </c>
-      <c r="F92" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>20330051920068</v>
-      </c>
-      <c r="B93" t="s">
-        <v>89</v>
-      </c>
-      <c r="C93" t="s">
-        <v>73</v>
-      </c>
-      <c r="D93" t="s">
-        <v>145</v>
-      </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>20330051920068</v>
-      </c>
-      <c r="B94" t="s">
-        <v>89</v>
-      </c>
-      <c r="C94" t="s">
-        <v>73</v>
-      </c>
-      <c r="D94" t="s">
-        <v>145</v>
-      </c>
-      <c r="E94" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920068</v>
-      </c>
-      <c r="B95" t="s">
-        <v>89</v>
-      </c>
-      <c r="C95" t="s">
-        <v>73</v>
-      </c>
-      <c r="D95" t="s">
-        <v>145</v>
-      </c>
-      <c r="E95" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>20330051920070</v>
-      </c>
-      <c r="B96" t="s">
-        <v>89</v>
-      </c>
-      <c r="C96" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" t="s">
-        <v>146</v>
-      </c>
-      <c r="E96" t="s">
-        <v>6</v>
-      </c>
-      <c r="F96" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>20330051920070</v>
-      </c>
-      <c r="B97" t="s">
-        <v>89</v>
-      </c>
-      <c r="C97" t="s">
-        <v>116</v>
-      </c>
-      <c r="D97" t="s">
-        <v>146</v>
-      </c>
-      <c r="E97" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>20330051920070</v>
-      </c>
-      <c r="B98" t="s">
-        <v>89</v>
-      </c>
-      <c r="C98" t="s">
-        <v>116</v>
-      </c>
-      <c r="D98" t="s">
-        <v>146</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>20330051920070</v>
-      </c>
-      <c r="B99" t="s">
-        <v>89</v>
-      </c>
-      <c r="C99" t="s">
-        <v>116</v>
-      </c>
-      <c r="D99" t="s">
-        <v>146</v>
-      </c>
-      <c r="E99" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>20330051920069</v>
-      </c>
-      <c r="B100" t="s">
-        <v>90</v>
-      </c>
-      <c r="C100" t="s">
-        <v>117</v>
-      </c>
-      <c r="D100" t="s">
-        <v>147</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>20330051920069</v>
-      </c>
-      <c r="B101" t="s">
-        <v>90</v>
-      </c>
-      <c r="C101" t="s">
-        <v>117</v>
-      </c>
-      <c r="D101" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>20330051920069</v>
-      </c>
-      <c r="B102" t="s">
-        <v>90</v>
-      </c>
-      <c r="C102" t="s">
-        <v>117</v>
-      </c>
-      <c r="D102" t="s">
-        <v>147</v>
-      </c>
-      <c r="E102" t="s">
-        <v>9</v>
-      </c>
-      <c r="F102" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>20330051920386</v>
-      </c>
-      <c r="B103" t="s">
-        <v>91</v>
-      </c>
-      <c r="C103" t="s">
-        <v>118</v>
-      </c>
-      <c r="D103" t="s">
-        <v>148</v>
-      </c>
-      <c r="E103" t="s">
-        <v>7</v>
-      </c>
-      <c r="F103" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>20330051920386</v>
-      </c>
-      <c r="B104" t="s">
-        <v>91</v>
-      </c>
-      <c r="C104" t="s">
-        <v>118</v>
-      </c>
-      <c r="D104" t="s">
-        <v>148</v>
-      </c>
-      <c r="E104" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>20330051920386</v>
-      </c>
-      <c r="B105" t="s">
-        <v>91</v>
-      </c>
-      <c r="C105" t="s">
-        <v>118</v>
-      </c>
-      <c r="D105" t="s">
-        <v>148</v>
-      </c>
-      <c r="E105" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6124,13 +5413,13 @@
         <v>20330051920072</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E2">
         <v>6</v>
@@ -6141,13 +5430,13 @@
         <v>20330051920074</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -6158,13 +5447,13 @@
         <v>20330051920071</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -6172,16 +5461,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920073</v>
+        <v>20330051920077</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
         <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -6189,16 +5478,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920077</v>
+        <v>20330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -6206,16 +5495,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920084</v>
+        <v>20330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -6223,67 +5512,67 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920088</v>
+        <v>20330051920073</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920089</v>
+        <v>20330051920084</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920070</v>
+        <v>20330051920088</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920041</v>
+        <v>20330051920092</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -6291,16 +5580,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920359</v>
+        <v>20330051920059</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -6311,16 +5600,16 @@
         <v>20330051920075</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -6328,322 +5617,322 @@
         <v>20330051920080</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920081</v>
+        <v>20330051920087</v>
       </c>
       <c r="B15" t="s">
         <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920082</v>
+        <v>20330051920061</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920087</v>
+        <v>20330051920065</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920090</v>
+        <v>20330051920066</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920091</v>
+        <v>20330051920068</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920092</v>
+        <v>20330051920069</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920093</v>
+        <v>20330051920386</v>
       </c>
       <c r="B21" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920059</v>
+        <v>19330051920051</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920061</v>
+        <v>20330051920081</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920062</v>
+        <v>20330051920082</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920063</v>
+        <v>20330051920091</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920064</v>
+        <v>20330051920093</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920065</v>
+        <v>20330051920062</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920066</v>
+        <v>20330051920063</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920068</v>
+        <v>20330051920064</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920069</v>
+        <v>20330051920041</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920386</v>
+        <v>20330051920359</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920051</v>
+        <v>20330051920090</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6653,7 +5942,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6683,6 +5972,443 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920051</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920051</v>
+      </c>
+      <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920087</v>
+      </c>
+      <c r="B4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920087</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920091</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920091</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920065</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920065</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920068</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920068</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920069</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920069</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>140</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920359</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920081</v>
+      </c>
+      <c r="B15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920082</v>
+      </c>
+      <c r="B16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>124</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920093</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920062</v>
+      </c>
+      <c r="B18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920063</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>134</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920064</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -990,7 +990,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1346,7 +1346,7 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1388,7 +1388,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1566,7 +1566,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>-1</v>
@@ -1675,7 +1675,7 @@
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -1738,7 +1738,7 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>-1</v>
@@ -2031,7 +2031,7 @@
         <v>-1</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F16">
         <v>8</v>
@@ -2046,7 +2046,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2094,7 +2094,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -2491,7 +2491,7 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2669,7 +2669,7 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2832,7 +2832,7 @@
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>6</v>
@@ -2895,7 +2895,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <v>6</v>
@@ -2936,7 +2936,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2978,7 +2978,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>-1</v>
@@ -3277,7 +3277,7 @@
         <v>-1</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
         <v>6</v>
@@ -3340,7 +3340,7 @@
         <v>-1</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -3559,7 +3559,7 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3601,7 +3601,7 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>-1</v>
@@ -3648,7 +3648,7 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3802,25 +3802,25 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="G3">
         <v>3.33</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3942,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4471,10 +4471,10 @@
         <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4491,30 +4491,30 @@
         <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920077</v>
+        <v>20330051920080</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4531,44 +4531,44 @@
         <v>122</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920080</v>
+        <v>20330051920081</v>
       </c>
       <c r="B28" t="s">
         <v>71</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B29" t="s">
         <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E29" t="s">
         <v>7</v>
@@ -4579,16 +4579,16 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920082</v>
+        <v>20330051920084</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E30" t="s">
         <v>7</v>
@@ -4611,64 +4611,64 @@
         <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920084</v>
+        <v>20330051920087</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920084</v>
+        <v>20330051920087</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920087</v>
+        <v>20330051920088</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -4679,16 +4679,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920087</v>
+        <v>20330051920088</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -4711,50 +4711,50 @@
         <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920088</v>
+        <v>20330051920089</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920088</v>
+        <v>20330051920089</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4771,10 +4771,10 @@
         <v>128</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4791,70 +4791,70 @@
         <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920089</v>
+        <v>20330051920091</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920089</v>
+        <v>20330051920092</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920091</v>
+        <v>20330051920092</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4871,70 +4871,70 @@
         <v>129</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920092</v>
+        <v>20330051920093</v>
       </c>
       <c r="B45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920092</v>
+        <v>20330051920059</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C46" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D46" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920093</v>
+        <v>20330051920059</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4951,64 +4951,64 @@
         <v>131</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920059</v>
+        <v>20330051920061</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920059</v>
+        <v>20330051920062</v>
       </c>
       <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="s">
         <v>79</v>
       </c>
-      <c r="C50" t="s">
-        <v>106</v>
-      </c>
       <c r="D50" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920061</v>
+        <v>20330051920063</v>
       </c>
       <c r="B51" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -5019,36 +5019,36 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920061</v>
+        <v>20330051920064</v>
       </c>
       <c r="B52" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D52" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920062</v>
+        <v>20330051920065</v>
       </c>
       <c r="B53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="D53" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
@@ -5059,36 +5059,36 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920063</v>
+        <v>20330051920065</v>
       </c>
       <c r="B54" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E54" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>20330051920064</v>
+        <v>20330051920066</v>
       </c>
       <c r="B55" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C55" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D55" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E55" t="s">
         <v>7</v>
@@ -5099,16 +5099,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>20330051920065</v>
+        <v>20330051920068</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="D56" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -5119,16 +5119,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>20330051920065</v>
+        <v>20330051920068</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C57" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5139,241 +5139,161 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>20330051920066</v>
+        <v>20330051920070</v>
       </c>
       <c r="B58" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D58" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F58" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>20330051920066</v>
+        <v>20330051920070</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C59" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>20330051920068</v>
+        <v>20330051920070</v>
       </c>
       <c r="B60" t="s">
         <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E60" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>20330051920068</v>
+        <v>20330051920070</v>
       </c>
       <c r="B61" t="s">
         <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>20330051920070</v>
+        <v>20330051920069</v>
       </c>
       <c r="B62" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E62" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F62" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>20330051920070</v>
+        <v>20330051920069</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E63" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920070</v>
+        <v>20330051920386</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920070</v>
+        <v>20330051920386</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D65" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E65" t="s">
         <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920069</v>
-      </c>
-      <c r="B66" t="s">
-        <v>87</v>
-      </c>
-      <c r="C66" t="s">
-        <v>113</v>
-      </c>
-      <c r="D66" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920069</v>
-      </c>
-      <c r="B67" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" t="s">
-        <v>113</v>
-      </c>
-      <c r="D67" t="s">
-        <v>140</v>
-      </c>
-      <c r="E67" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920386</v>
-      </c>
-      <c r="B68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" t="s">
-        <v>141</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920386</v>
-      </c>
-      <c r="B69" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" t="s">
-        <v>141</v>
-      </c>
-      <c r="E69" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" t="s">
         <v>57</v>
       </c>
     </row>
@@ -5461,16 +5381,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920077</v>
+        <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -5478,16 +5398,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920089</v>
+        <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -5495,33 +5415,33 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920070</v>
+        <v>20330051920073</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920073</v>
+        <v>20330051920077</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -5529,16 +5449,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920084</v>
+        <v>20330051920088</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -5546,16 +5466,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920088</v>
+        <v>20330051920092</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -5563,16 +5483,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920092</v>
+        <v>20330051920059</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -5580,33 +5500,33 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920059</v>
+        <v>20330051920075</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5614,16 +5534,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920080</v>
+        <v>20330051920084</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5648,16 +5568,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920061</v>
+        <v>20330051920065</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E16">
         <v>2</v>
@@ -5665,16 +5585,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920065</v>
+        <v>20330051920068</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="D17" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -5682,16 +5602,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920066</v>
+        <v>20330051920069</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E18">
         <v>2</v>
@@ -5699,16 +5619,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920068</v>
+        <v>20330051920386</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E19">
         <v>2</v>
@@ -5716,50 +5636,50 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920069</v>
+        <v>19330051920051</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920386</v>
+        <v>20330051920081</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -5767,16 +5687,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920081</v>
+        <v>20330051920091</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -5784,16 +5704,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920082</v>
+        <v>20330051920093</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5801,16 +5721,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920091</v>
+        <v>20330051920061</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -5818,16 +5738,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920093</v>
+        <v>20330051920062</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -5835,16 +5755,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920062</v>
+        <v>20330051920063</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -5852,16 +5772,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920063</v>
+        <v>20330051920064</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -5869,16 +5789,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920064</v>
+        <v>20330051920066</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -5942,7 +5862,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6158,16 +6078,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920068</v>
+        <v>20330051920066</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6181,39 +6101,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920068</v>
+        <v>20330051920066</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920069</v>
+        <v>20330051920068</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -6227,22 +6147,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920069</v>
+        <v>20330051920068</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -6250,45 +6170,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920359</v>
+        <v>20330051920069</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920081</v>
+        <v>20330051920069</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -6296,39 +6216,39 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920082</v>
+        <v>20330051920359</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920093</v>
+        <v>20330051920081</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -6342,16 +6262,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920062</v>
+        <v>20330051920082</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -6365,16 +6285,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920063</v>
+        <v>20330051920093</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -6388,16 +6308,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920064</v>
+        <v>20330051920062</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -6406,6 +6326,52 @@
         <v>53</v>
       </c>
       <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920063</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920064</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -185,21 +185,21 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
+    <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,39 +227,159 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>ESPINOZA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>GUILLEN</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>OLMOS</t>
   </si>
   <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
@@ -272,45 +392,12 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
     <t>SILVESTRE</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>MENDEZ</t>
   </si>
   <si>
@@ -320,27 +407,15 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
+    <t>BAROJAS</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ALAMILLO</t>
   </si>
   <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
@@ -350,45 +425,18 @@
     <t>VELASCO</t>
   </si>
   <si>
-    <t>URBINA</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
   </si>
   <si>
     <t>JESUS ISRAEL</t>
   </si>
   <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
     <t>CRISTIAN JAHIR</t>
   </si>
   <si>
@@ -398,24 +446,12 @@
     <t>ANGEL</t>
   </si>
   <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
+    <t>DIEGO IVAN</t>
   </si>
   <si>
     <t>JOHAN ALEJANDRO</t>
   </si>
   <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
     <t>ALAN URIEL</t>
   </si>
   <si>
@@ -428,43 +464,7 @@
     <t>JORGE ALEJANDRO</t>
   </si>
   <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
     <t>YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
   </si>
 </sst>
 </file>
@@ -987,25 +987,25 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1029,7 +1029,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1041,10 +1041,10 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC4">
         <v>8</v>
@@ -1061,7 +1061,7 @@
         <v>-1</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>-1</v>
@@ -1076,13 +1076,13 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1091,10 +1091,10 @@
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1118,13 +1118,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <v>-1</v>
@@ -1133,7 +1133,7 @@
         <v>-1</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1150,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>-1</v>
@@ -1162,16 +1162,16 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1180,10 +1180,10 @@
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1213,7 +1213,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z6">
         <v>-1</v>
@@ -1222,10 +1222,10 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1233,13 +1233,13 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>-1</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>-1</v>
@@ -1251,16 +1251,16 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1269,10 +1269,10 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1296,13 +1296,13 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <v>-1</v>
@@ -1314,7 +1314,7 @@
         <v>5</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1343,25 +1343,25 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1385,13 +1385,13 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1400,7 +1400,7 @@
         <v>10</v>
       </c>
       <c r="AB8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>8</v>
@@ -1411,13 +1411,13 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>-1</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -1432,13 +1432,13 @@
         <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1447,10 +1447,10 @@
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1474,13 +1474,13 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>-1</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>-1</v>
@@ -1506,7 +1506,7 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1521,13 +1521,13 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1536,10 +1536,10 @@
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1563,13 +1563,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>10</v>
@@ -1578,7 +1578,7 @@
         <v>-1</v>
       </c>
       <c r="AB10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1595,7 +1595,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -1607,22 +1607,22 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1649,16 +1649,16 @@
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>6</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1672,7 +1672,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -1684,16 +1684,16 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1702,10 +1702,10 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1735,7 +1735,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1744,10 +1744,10 @@
         <v>-1</v>
       </c>
       <c r="AB12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1761,7 +1761,7 @@
         <v>6</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E13">
         <v>-1</v>
@@ -1776,13 +1776,13 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1791,10 +1791,10 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1818,13 +1818,13 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>-1</v>
@@ -1836,7 +1836,7 @@
         <v>5</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1850,7 +1850,7 @@
         <v>8</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>6</v>
@@ -1865,13 +1865,13 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1880,10 +1880,10 @@
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1907,13 +1907,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <v>6</v>
@@ -1922,7 +1922,7 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -1939,7 +1939,7 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>7</v>
@@ -1954,25 +1954,25 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1996,13 +1996,13 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>7</v>
@@ -2028,7 +2028,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E16">
         <v>6</v>
@@ -2037,19 +2037,19 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -2058,10 +2058,10 @@
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2085,13 +2085,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2100,7 +2100,7 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2117,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>-1</v>
@@ -2132,13 +2132,13 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2147,10 +2147,10 @@
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2180,7 +2180,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <v>-1</v>
@@ -2189,7 +2189,7 @@
         <v>6</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>6</v>
@@ -2206,7 +2206,7 @@
         <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>-1</v>
@@ -2215,19 +2215,19 @@
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2236,10 +2236,10 @@
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2269,7 +2269,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>-1</v>
@@ -2278,7 +2278,7 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2295,7 +2295,7 @@
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>-1</v>
@@ -2310,13 +2310,13 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2325,10 +2325,10 @@
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2352,13 +2352,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z19">
         <v>-1</v>
@@ -2370,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2399,25 +2399,25 @@
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2441,13 +2441,13 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>7</v>
@@ -2456,10 +2456,10 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2473,7 +2473,7 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -2488,25 +2488,25 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2530,19 +2530,19 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>7</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E22">
         <v>-1</v>
@@ -2577,13 +2577,13 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2592,10 +2592,10 @@
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2619,13 +2619,13 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z22">
         <v>-1</v>
@@ -2651,7 +2651,7 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>9</v>
@@ -2666,25 +2666,25 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2708,25 +2708,25 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2740,7 +2740,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>-1</v>
@@ -2755,13 +2755,13 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2770,10 +2770,10 @@
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2803,7 +2803,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z24">
         <v>-1</v>
@@ -2829,7 +2829,7 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>6</v>
@@ -2844,25 +2844,25 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2886,13 +2886,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2901,10 +2901,10 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2918,7 +2918,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>7</v>
@@ -2933,25 +2933,25 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2981,16 +2981,16 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -3007,7 +3007,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>10</v>
@@ -3022,25 +3022,25 @@
         <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3064,13 +3064,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z27">
         <v>10</v>
@@ -3096,7 +3096,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
         <v>7</v>
@@ -3111,13 +3111,13 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -3126,10 +3126,10 @@
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3153,13 +3153,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -3168,7 +3168,7 @@
         <v>8</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3185,7 +3185,7 @@
         <v>6</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E29">
         <v>-1</v>
@@ -3200,13 +3200,13 @@
         <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3215,10 +3215,10 @@
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3242,13 +3242,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z29">
         <v>-1</v>
@@ -3260,7 +3260,7 @@
         <v>6</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -3289,25 +3289,25 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3331,13 +3331,13 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X30">
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3346,7 +3346,7 @@
         <v>6</v>
       </c>
       <c r="AB30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC30">
         <v>7</v>
@@ -3363,7 +3363,7 @@
         <v>6</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>-1</v>
@@ -3378,25 +3378,25 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3420,22 +3420,22 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z31">
         <v>-1</v>
       </c>
       <c r="AA31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
         <v>7</v>
@@ -3452,7 +3452,7 @@
         <v>-1</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E32">
         <v>-1</v>
@@ -3467,13 +3467,13 @@
         <v>6</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3482,10 +3482,10 @@
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3509,13 +3509,13 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>-1</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z32">
         <v>-1</v>
@@ -3524,7 +3524,7 @@
         <v>-1</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC32">
         <v>6</v>
@@ -3541,7 +3541,7 @@
         <v>6</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -3556,13 +3556,13 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3571,10 +3571,10 @@
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3604,7 +3604,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z33">
         <v>6</v>
@@ -3616,7 +3616,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3630,7 +3630,7 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -3645,13 +3645,13 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
         <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3660,10 +3660,10 @@
         <v>-1</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3687,13 +3687,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z34">
         <v>7</v>
@@ -3702,7 +3702,7 @@
         <v>-1</v>
       </c>
       <c r="AB34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC34">
         <v>5</v>
@@ -3770,25 +3770,25 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E2">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>32.26</v>
+      </c>
+      <c r="G2">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="H2">
+        <v>5.6</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>9.68</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.3</v>
-      </c>
-      <c r="I2">
-        <v>28</v>
-      </c>
-      <c r="J2">
-        <v>90.31999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3825,7 +3825,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3834,30 +3834,30 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>64.52</v>
+        <v>61.29</v>
       </c>
       <c r="G4">
-        <v>29.03</v>
+        <v>38.71</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3869,27 +3869,27 @@
         <v>20</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>64.52</v>
       </c>
       <c r="G5">
-        <v>25.81</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J5">
-        <v>9.68</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
@@ -3898,30 +3898,30 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="G6">
+        <v>32.26</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>64.52</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.7</v>
-      </c>
-      <c r="I6">
-        <v>11</v>
-      </c>
-      <c r="J6">
-        <v>35.48</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3930,30 +3930,30 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E7">
+        <v>9</v>
+      </c>
+      <c r="F7">
+        <v>70.97</v>
+      </c>
+      <c r="G7">
+        <v>29.03</v>
+      </c>
+      <c r="H7">
+        <v>6.6</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>83.87</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>16.13</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -3962,25 +3962,25 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>93.55</v>
+        <v>83.87</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>6.45</v>
+        <v>16.13</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4025,16 +4025,16 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4045,16 +4045,16 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4065,36 +4065,36 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4105,16 +4105,16 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4125,213 +4125,213 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920072</v>
+        <v>20330051920073</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920073</v>
+        <v>20330051920075</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920073</v>
+        <v>20330051920077</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920073</v>
+        <v>20330051920080</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920074</v>
+        <v>20330051920087</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920074</v>
+        <v>20330051920088</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920074</v>
+        <v>20330051920089</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>59</v>
@@ -4339,16 +4339,16 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920074</v>
+        <v>20330051920089</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4359,176 +4359,176 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920074</v>
+        <v>20330051920089</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920075</v>
+        <v>20330051920092</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920075</v>
+        <v>20330051920092</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920051</v>
+        <v>20330051920059</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920077</v>
+        <v>20330051920059</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920077</v>
+        <v>20330051920065</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920077</v>
+        <v>20330051920068</v>
       </c>
       <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
         <v>70</v>
       </c>
-      <c r="C25" t="s">
-        <v>95</v>
-      </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920080</v>
+        <v>20330051920070</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920080</v>
+        <v>20330051920070</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -4539,762 +4539,62 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920081</v>
+        <v>20330051920070</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920082</v>
+        <v>20330051920069</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920084</v>
+        <v>20330051920386</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920084</v>
-      </c>
-      <c r="B31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" t="s">
-        <v>125</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920087</v>
-      </c>
-      <c r="B32" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" t="s">
-        <v>126</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920087</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" t="s">
-        <v>100</v>
-      </c>
-      <c r="D33" t="s">
-        <v>126</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920088</v>
-      </c>
-      <c r="B34" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920088</v>
-      </c>
-      <c r="B35" t="s">
-        <v>74</v>
-      </c>
-      <c r="C35" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920088</v>
-      </c>
-      <c r="B36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>20330051920089</v>
-      </c>
-      <c r="B37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C37" t="s">
-        <v>102</v>
-      </c>
-      <c r="D37" t="s">
-        <v>128</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920089</v>
-      </c>
-      <c r="B38" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920089</v>
-      </c>
-      <c r="B39" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" t="s">
-        <v>102</v>
-      </c>
-      <c r="D39" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920089</v>
-      </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D40" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920091</v>
-      </c>
-      <c r="B41" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>103</v>
-      </c>
-      <c r="D41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920092</v>
-      </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C42" t="s">
-        <v>104</v>
-      </c>
-      <c r="D42" t="s">
-        <v>129</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920092</v>
-      </c>
-      <c r="B43" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" t="s">
-        <v>104</v>
-      </c>
-      <c r="D43" t="s">
-        <v>129</v>
-      </c>
-      <c r="E43" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>20330051920092</v>
-      </c>
-      <c r="B44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C44" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" t="s">
-        <v>129</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>20330051920093</v>
-      </c>
-      <c r="B45" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920059</v>
-      </c>
-      <c r="B46" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D46" t="s">
-        <v>131</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920059</v>
-      </c>
-      <c r="B47" t="s">
-        <v>79</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920059</v>
-      </c>
-      <c r="B48" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" t="s">
-        <v>131</v>
-      </c>
-      <c r="E48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920061</v>
-      </c>
-      <c r="B49" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" t="s">
-        <v>132</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920062</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" t="s">
-        <v>79</v>
-      </c>
-      <c r="D50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920063</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" t="s">
-        <v>134</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920064</v>
-      </c>
-      <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" t="s">
-        <v>109</v>
-      </c>
-      <c r="D52" t="s">
-        <v>135</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920065</v>
-      </c>
-      <c r="B53" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" t="s">
-        <v>110</v>
-      </c>
-      <c r="D53" t="s">
-        <v>136</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920065</v>
-      </c>
-      <c r="B54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" t="s">
-        <v>110</v>
-      </c>
-      <c r="D54" t="s">
-        <v>136</v>
-      </c>
-      <c r="E54" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920066</v>
-      </c>
-      <c r="B55" t="s">
-        <v>85</v>
-      </c>
-      <c r="C55" t="s">
-        <v>111</v>
-      </c>
-      <c r="D55" t="s">
-        <v>137</v>
-      </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920068</v>
-      </c>
-      <c r="B56" t="s">
-        <v>86</v>
-      </c>
-      <c r="C56" t="s">
-        <v>71</v>
-      </c>
-      <c r="D56" t="s">
-        <v>138</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920068</v>
-      </c>
-      <c r="B57" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" t="s">
-        <v>138</v>
-      </c>
-      <c r="E57" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>20330051920070</v>
-      </c>
-      <c r="B58" t="s">
-        <v>86</v>
-      </c>
-      <c r="C58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" t="s">
-        <v>139</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>20330051920070</v>
-      </c>
-      <c r="B59" t="s">
-        <v>86</v>
-      </c>
-      <c r="C59" t="s">
-        <v>112</v>
-      </c>
-      <c r="D59" t="s">
-        <v>139</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920070</v>
-      </c>
-      <c r="B60" t="s">
-        <v>86</v>
-      </c>
-      <c r="C60" t="s">
-        <v>112</v>
-      </c>
-      <c r="D60" t="s">
-        <v>139</v>
-      </c>
-      <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920070</v>
-      </c>
-      <c r="B61" t="s">
-        <v>86</v>
-      </c>
-      <c r="C61" t="s">
-        <v>112</v>
-      </c>
-      <c r="D61" t="s">
-        <v>139</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920069</v>
-      </c>
-      <c r="B62" t="s">
-        <v>87</v>
-      </c>
-      <c r="C62" t="s">
-        <v>113</v>
-      </c>
-      <c r="D62" t="s">
-        <v>140</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920069</v>
-      </c>
-      <c r="B63" t="s">
-        <v>87</v>
-      </c>
-      <c r="C63" t="s">
-        <v>113</v>
-      </c>
-      <c r="D63" t="s">
-        <v>140</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920386</v>
-      </c>
-      <c r="B64" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" t="s">
-        <v>141</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920386</v>
-      </c>
-      <c r="B65" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" t="s">
-        <v>141</v>
-      </c>
-      <c r="E65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -5330,53 +4630,53 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920072</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920074</v>
+        <v>20330051920072</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920071</v>
+        <v>20330051920074</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5384,16 +4684,16 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5401,418 +4701,418 @@
         <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920073</v>
+        <v>20330051920092</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920077</v>
+        <v>20330051920059</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920088</v>
+        <v>20330051920073</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920092</v>
+        <v>20330051920075</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920059</v>
+        <v>20330051920077</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920075</v>
+        <v>20330051920080</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920080</v>
+        <v>20330051920087</v>
       </c>
       <c r="B13" t="s">
         <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920084</v>
+        <v>20330051920088</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920087</v>
+        <v>20330051920065</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920065</v>
+        <v>20330051920068</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920068</v>
+        <v>20330051920069</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920069</v>
+        <v>20330051920386</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920386</v>
+        <v>20330051920041</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920051</v>
+        <v>20330051920359</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920081</v>
+        <v>19330051920051</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920082</v>
+        <v>20330051920081</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920091</v>
+        <v>20330051920082</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920093</v>
+        <v>20330051920084</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920061</v>
+        <v>20330051920090</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920062</v>
+        <v>20330051920091</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920063</v>
+        <v>20330051920093</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920064</v>
+        <v>20330051920061</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920066</v>
+        <v>20330051920062</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="C29" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920041</v>
+        <v>20330051920063</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -5823,13 +5123,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920359</v>
+        <v>20330051920064</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -5840,13 +5140,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920090</v>
+        <v>20330051920066</v>
       </c>
       <c r="B32" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -5862,7 +5162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5894,16 +5194,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920087</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5912,90 +5212,90 @@
         <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920051</v>
+        <v>20330051920087</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920087</v>
+        <v>20330051920061</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920091</v>
+        <v>20330051920065</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -6004,21 +5304,21 @@
         <v>53</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920091</v>
+        <v>20330051920065</v>
       </c>
       <c r="B7" t="s">
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6027,67 +5327,67 @@
         <v>54</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920065</v>
+        <v>20330051920066</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920065</v>
+        <v>20330051920066</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920066</v>
+        <v>19330051920051</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="C10" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6096,24 +5396,24 @@
         <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920066</v>
+        <v>20330051920090</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>55</v>
@@ -6124,254 +5424,70 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920068</v>
+        <v>20330051920091</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920068</v>
+        <v>20330051920063</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920069</v>
+        <v>20330051920068</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920069</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920359</v>
-      </c>
-      <c r="B16" t="s">
-        <v>143</v>
-      </c>
-      <c r="C16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920081</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920082</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920093</v>
-      </c>
-      <c r="B19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>130</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920062</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920063</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920064</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -218,253 +218,253 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>ESPINOZA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
     <t>CANUTO</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>ESPINOZA</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
   </si>
   <si>
     <t>MEDINA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AXEL JESUS</t>
   </si>
   <si>
     <t>ISRAEL</t>
   </si>
   <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
   </si>
   <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
   </si>
   <si>
     <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
   </si>
 </sst>
 </file>
@@ -996,7 +996,7 @@
         <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1153,7 +1153,7 @@
         <v>4</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -1174,7 +1174,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1216,7 +1216,7 @@
         <v>5</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1352,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1394,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1764,7 +1764,7 @@
         <v>4</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -1827,7 +1827,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1874,10 +1874,10 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -1916,7 +1916,7 @@
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1963,7 +1963,7 @@
         <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>7</v>
@@ -2005,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -2497,7 +2497,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -2539,7 +2539,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2942,7 +2942,7 @@
         <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2984,7 +2984,7 @@
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>9</v>
@@ -3120,7 +3120,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -3298,7 +3298,7 @@
         <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>6</v>
@@ -3366,7 +3366,7 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F31">
         <v>8</v>
@@ -3387,7 +3387,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>6</v>
@@ -3429,7 +3429,7 @@
         <v>6</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3455,7 +3455,7 @@
         <v>4</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F32">
         <v>-1</v>
@@ -3476,7 +3476,7 @@
         <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3518,7 +3518,7 @@
         <v>5</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA32">
         <v>-1</v>
@@ -3565,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3607,7 +3607,7 @@
         <v>5</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>-1</v>
@@ -3793,39 +3793,39 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>53.33</v>
+        <v>61.29</v>
       </c>
       <c r="G3">
-        <v>3.33</v>
+        <v>38.71</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>43.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3834,30 +3834,30 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>61.29</v>
+        <v>64.52</v>
       </c>
       <c r="G4">
-        <v>38.71</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3866,57 +3866,57 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="G5">
+        <v>32.26</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>64.52</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.6</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>35.48</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>21</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>67.73999999999999</v>
+        <v>70</v>
       </c>
       <c r="G6">
-        <v>32.26</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4025,10 +4025,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4045,16 +4045,16 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4065,16 +4065,16 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4085,10 +4085,10 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -4105,16 +4105,16 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4125,36 +4125,36 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920073</v>
+        <v>20330051920074</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4162,19 +4162,19 @@
         <v>20330051920074</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4182,139 +4182,139 @@
         <v>20330051920074</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920074</v>
+        <v>20330051920075</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B12" t="s">
         <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920077</v>
+        <v>20330051920087</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920080</v>
+        <v>20330051920088</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920087</v>
+        <v>20330051920089</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920088</v>
+        <v>20330051920089</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4322,279 +4322,199 @@
         <v>20330051920089</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920089</v>
+        <v>20330051920092</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920089</v>
+        <v>20330051920092</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920092</v>
+        <v>20330051920059</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920092</v>
+        <v>20330051920059</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920059</v>
+        <v>20330051920065</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920059</v>
+        <v>20330051920070</v>
       </c>
       <c r="B23" t="s">
         <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920065</v>
+        <v>20330051920070</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920068</v>
+        <v>20330051920069</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920070</v>
+        <v>20330051920386</v>
       </c>
       <c r="B26" t="s">
         <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920070</v>
-      </c>
-      <c r="B27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920070</v>
-      </c>
-      <c r="B28" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>20330051920069</v>
-      </c>
-      <c r="B29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920386</v>
-      </c>
-      <c r="B30" t="s">
-        <v>79</v>
-      </c>
-      <c r="C30" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" t="s">
-        <v>112</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4636,10 +4556,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4653,10 +4573,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -4667,13 +4587,13 @@
         <v>20330051920074</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -4684,13 +4604,13 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4698,33 +4618,33 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920070</v>
+        <v>20330051920092</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920092</v>
+        <v>20330051920059</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4732,16 +4652,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920059</v>
+        <v>20330051920070</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4749,16 +4669,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920073</v>
+        <v>20330051920075</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4766,16 +4686,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4783,16 +4703,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920077</v>
+        <v>20330051920087</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4800,16 +4720,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920080</v>
+        <v>20330051920088</v>
       </c>
       <c r="B12" t="s">
         <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4817,16 +4737,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920087</v>
+        <v>20330051920065</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4834,13 +4754,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920088</v>
+        <v>20330051920069</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>104</v>
@@ -4851,16 +4771,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920065</v>
+        <v>20330051920386</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4868,64 +4788,64 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920068</v>
+        <v>20330051920041</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920069</v>
+        <v>20330051920073</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920386</v>
+        <v>20330051920359</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920041</v>
+        <v>19330051920051</v>
       </c>
       <c r="B19" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
         <v>136</v>
@@ -4936,13 +4856,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920359</v>
+        <v>20330051920080</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
         <v>137</v>
@@ -4953,13 +4873,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920051</v>
+        <v>20330051920081</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>138</v>
@@ -4970,13 +4890,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="C22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
         <v>139</v>
@@ -4987,13 +4907,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920082</v>
+        <v>20330051920084</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -5004,13 +4924,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920084</v>
+        <v>20330051920090</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
         <v>141</v>
@@ -5021,16 +4941,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920090</v>
+        <v>20330051920091</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5038,16 +4958,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920091</v>
+        <v>20330051920093</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D26" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5055,13 +4975,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920093</v>
+        <v>20330051920061</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C27" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
         <v>143</v>
@@ -5072,13 +4992,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920061</v>
+        <v>20330051920062</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
@@ -5089,13 +5009,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920062</v>
+        <v>20330051920063</v>
       </c>
       <c r="B29" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -5106,13 +5026,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920063</v>
+        <v>20330051920064</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -5123,13 +5043,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920064</v>
+        <v>20330051920066</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -5140,13 +5060,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920066</v>
+        <v>20330051920068</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -5194,16 +5114,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920087</v>
+        <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5217,45 +5137,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920087</v>
+        <v>20330051920073</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5263,45 +5183,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920061</v>
+        <v>20330051920087</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920065</v>
+        <v>20330051920061</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5309,45 +5229,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920065</v>
+        <v>20330051920061</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920066</v>
+        <v>20330051920065</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5355,45 +5275,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920066</v>
+        <v>20330051920065</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920051</v>
+        <v>20330051920066</v>
       </c>
       <c r="B10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5401,22 +5321,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920090</v>
+        <v>20330051920066</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5424,22 +5344,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920091</v>
+        <v>19330051920051</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5447,22 +5367,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920063</v>
+        <v>20330051920090</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="D13" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5470,25 +5390,25 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920068</v>
+        <v>20330051920063</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -179,27 +179,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -227,46 +227,157 @@
     <t>ESPINOZA</t>
   </si>
   <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CASTAÑEDA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>EVARISTO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JOAQUIN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>PAUL ARAVIER</t>
+  </si>
+  <si>
+    <t>NORKYS AIRY</t>
+  </si>
+  <si>
+    <t>JORGE HUMBERTO</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
     <t>MAYAHUA</t>
   </si>
   <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZGAIP</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CASTAÑEDA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
@@ -275,40 +386,52 @@
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
   </si>
   <si>
     <t>URBINA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>PAUL ARAVIER</t>
-  </si>
-  <si>
-    <t>NORKYS AIRY</t>
-  </si>
-  <si>
-    <t>JORGE HUMBERTO</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
   </si>
   <si>
     <t>GABRIEL JOSUE</t>
@@ -317,148 +440,25 @@
     <t>ELIAS</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
   </si>
   <si>
     <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>OSVALDO</t>
-  </si>
-  <si>
-    <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
   </si>
   <si>
     <t>YAIR</t>
@@ -1008,28 +1008,28 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>-1</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1064,7 +1064,7 @@
         <v>4</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -1085,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1097,22 +1097,22 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>-1</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1127,13 +1127,13 @@
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA5">
         <v>-1</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1186,22 +1186,22 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>-1</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1213,7 +1213,7 @@
         <v>6</v>
       </c>
       <c r="Y6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <v>7</v>
@@ -1222,7 +1222,7 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>5</v>
@@ -1242,7 +1242,7 @@
         <v>4</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -1263,7 +1263,7 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1275,22 +1275,22 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>-1</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1302,10 +1302,10 @@
         <v>-1</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA7">
         <v>-1</v>
@@ -1364,28 +1364,28 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>-1</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>4</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -1441,7 +1441,7 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1453,43 +1453,43 @@
         <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>-1</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA9">
         <v>-1</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1542,43 +1542,43 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>-1</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>8</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>-1</v>
       </c>
       <c r="AB10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>5</v>
@@ -1625,19 +1625,19 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1655,7 +1655,7 @@
         <v>6</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1696,7 +1696,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1708,22 +1708,22 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>-1</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -1735,7 +1735,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1744,7 +1744,7 @@
         <v>-1</v>
       </c>
       <c r="AB12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1785,7 +1785,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1797,43 +1797,43 @@
         <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>-1</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1886,22 +1886,22 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>-1</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -1913,7 +1913,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>7</v>
@@ -1922,7 +1922,7 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>6</v>
@@ -1975,22 +1975,22 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>-1</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -2052,7 +2052,7 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2064,13 +2064,13 @@
         <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2079,7 +2079,7 @@
         <v>-1</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -2094,7 +2094,7 @@
         <v>5</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -2120,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -2141,7 +2141,7 @@
         <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2153,22 +2153,22 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>-1</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2180,10 +2180,10 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>6</v>
@@ -2209,7 +2209,7 @@
         <v>4</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>6</v>
@@ -2230,7 +2230,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2242,13 +2242,13 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2257,13 +2257,13 @@
         <v>-1</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>6</v>
@@ -2272,7 +2272,7 @@
         <v>5</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2298,7 +2298,7 @@
         <v>4</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>-1</v>
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2331,13 +2331,13 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2346,28 +2346,28 @@
         <v>-1</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>-1</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>-1</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>6</v>
@@ -2408,7 +2408,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>7</v>
@@ -2420,28 +2420,28 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>-1</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2456,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC20">
         <v>5</v>
@@ -2509,22 +2509,22 @@
         <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
         <v>-1</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -2565,7 +2565,7 @@
         <v>4</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>-1</v>
@@ -2586,7 +2586,7 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2598,13 +2598,13 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2613,7 +2613,7 @@
         <v>-1</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -2628,7 +2628,7 @@
         <v>5</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA22">
         <v>-1</v>
@@ -2687,22 +2687,22 @@
         <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>-1</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2717,13 +2717,13 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -2743,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -2764,7 +2764,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2776,22 +2776,22 @@
         <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>-1</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2803,10 +2803,10 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>-1</v>
@@ -2853,7 +2853,7 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>6</v>
@@ -2865,34 +2865,34 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
       </c>
       <c r="Y25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2954,22 +2954,22 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>-1</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -3031,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -3043,22 +3043,22 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>-1</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -3073,7 +3073,7 @@
         <v>7</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -3132,22 +3132,22 @@
         <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>-1</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -3159,7 +3159,7 @@
         <v>6</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -3168,7 +3168,7 @@
         <v>8</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>7</v>
@@ -3188,7 +3188,7 @@
         <v>4</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>6</v>
@@ -3209,7 +3209,7 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3221,37 +3221,37 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>-1</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -3310,34 +3310,34 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>-1</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>6</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3399,22 +3399,22 @@
         <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
         <v>-1</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -3426,10 +3426,10 @@
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>7</v>
@@ -3488,13 +3488,13 @@
         <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3503,19 +3503,19 @@
         <v>-1</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>-1</v>
       </c>
       <c r="Y32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z32">
         <v>7</v>
@@ -3524,7 +3524,7 @@
         <v>-1</v>
       </c>
       <c r="AB32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC32">
         <v>6</v>
@@ -3577,28 +3577,28 @@
         <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>-1</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3607,13 +3607,13 @@
         <v>5</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>-1</v>
       </c>
       <c r="AB33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC33">
         <v>5</v>
@@ -3654,7 +3654,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3666,13 +3666,13 @@
         <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3681,7 +3681,7 @@
         <v>-1</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3693,16 +3693,16 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA34">
         <v>-1</v>
       </c>
       <c r="AB34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC34">
         <v>5</v>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3770,19 +3770,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>32.26</v>
+        <v>61.29</v>
       </c>
       <c r="G2">
-        <v>67.73999999999999</v>
+        <v>38.71</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3802,30 +3802,30 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>61.29</v>
+        <v>64.52</v>
       </c>
       <c r="G3">
-        <v>38.71</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3834,30 +3834,30 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>77.42</v>
+      </c>
+      <c r="G4">
+        <v>22.58</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>64.52</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.6</v>
-      </c>
-      <c r="I4">
-        <v>11</v>
-      </c>
-      <c r="J4">
-        <v>35.48</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3866,19 +3866,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>67.73999999999999</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G5">
-        <v>32.26</v>
+        <v>19.35</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3898,30 +3898,30 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>83.33</v>
+      </c>
+      <c r="G6">
+        <v>16.67</v>
+      </c>
+      <c r="H6">
+        <v>6.7</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>70</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.4</v>
-      </c>
-      <c r="I6">
-        <v>9</v>
-      </c>
-      <c r="J6">
-        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3930,30 +3930,30 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>70.97</v>
+        <v>83.87</v>
       </c>
       <c r="G7">
-        <v>29.03</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -3962,25 +3962,25 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G8">
+        <v>12.9</v>
+      </c>
+      <c r="H8">
+        <v>6.6</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>83.87</v>
-      </c>
-      <c r="G8">
+      <c r="J8">
         <v>0</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
-      <c r="J8">
-        <v>16.13</v>
       </c>
     </row>
   </sheetData>
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4025,16 +4025,16 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4045,36 +4045,36 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920071</v>
+        <v>20330051920072</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4085,436 +4085,256 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920072</v>
+        <v>20330051920074</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920074</v>
+        <v>20330051920075</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920074</v>
+        <v>20330051920077</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920074</v>
+        <v>20330051920089</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920075</v>
+        <v>20330051920089</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920077</v>
+        <v>20330051920092</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920087</v>
+        <v>20330051920059</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920088</v>
+        <v>20330051920070</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920089</v>
+        <v>20330051920070</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920089</v>
+        <v>20330051920069</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920089</v>
+        <v>20330051920386</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
         <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920092</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920092</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920059</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920059</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920065</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920070</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920070</v>
-      </c>
-      <c r="B24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920069</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920386</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -4556,13 +4376,13 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4573,13 +4393,13 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4590,13 +4410,13 @@
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4604,30 +4424,30 @@
         <v>20330051920089</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920092</v>
+        <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4635,50 +4455,50 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920059</v>
+        <v>20330051920075</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920070</v>
+        <v>20330051920077</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920075</v>
+        <v>20330051920092</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4686,16 +4506,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920077</v>
+        <v>20330051920059</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4703,16 +4523,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920087</v>
+        <v>20330051920069</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4720,16 +4540,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920088</v>
+        <v>20330051920386</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4737,64 +4557,64 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920065</v>
+        <v>20330051920041</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920069</v>
+        <v>20330051920073</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920386</v>
+        <v>20330051920359</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920041</v>
+        <v>19330051920051</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -4805,13 +4625,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920073</v>
+        <v>20330051920080</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4822,13 +4642,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920359</v>
+        <v>20330051920081</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
         <v>135</v>
@@ -4839,13 +4659,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D19" t="s">
         <v>136</v>
@@ -4856,13 +4676,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920080</v>
+        <v>20330051920084</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>137</v>
@@ -4873,13 +4693,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920081</v>
+        <v>20330051920087</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>138</v>
@@ -4890,13 +4710,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920082</v>
+        <v>20330051920088</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>139</v>
@@ -4907,13 +4727,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920084</v>
+        <v>20330051920090</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
         <v>140</v>
@@ -4924,16 +4744,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920090</v>
+        <v>20330051920091</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4941,16 +4761,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920091</v>
+        <v>20330051920093</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4958,13 +4778,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920093</v>
+        <v>20330051920061</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D26" t="s">
         <v>142</v>
@@ -4975,13 +4795,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920061</v>
+        <v>20330051920062</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="D27" t="s">
         <v>143</v>
@@ -4992,13 +4812,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920062</v>
+        <v>20330051920063</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
@@ -5009,13 +4829,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920063</v>
+        <v>20330051920064</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -5026,13 +4846,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920064</v>
+        <v>20330051920065</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -5046,10 +4866,10 @@
         <v>20330051920066</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -5063,10 +4883,10 @@
         <v>20330051920068</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -5082,7 +4902,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5114,45 +4934,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920073</v>
+        <v>20330051920075</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920073</v>
+        <v>20330051920075</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5160,111 +4980,111 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920087</v>
+        <v>20330051920077</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920087</v>
+        <v>20330051920077</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920061</v>
+        <v>20330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920061</v>
+        <v>20330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920065</v>
+        <v>20330051920073</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
@@ -5275,45 +5095,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920065</v>
+        <v>19330051920051</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920066</v>
+        <v>20330051920080</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5321,19 +5141,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920066</v>
+        <v>20330051920090</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
@@ -5344,70 +5164,47 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920051</v>
+        <v>20330051920059</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920090</v>
+        <v>20330051920065</v>
       </c>
       <c r="B13" t="s">
         <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920063</v>
-      </c>
-      <c r="B14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -179,10 +179,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Muñoz Rivadeneyra Salvador</t>
@@ -1026,7 +1026,7 @@
         <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -1115,7 +1115,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -1204,7 +1204,7 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1225,7 +1225,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1293,7 +1293,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
@@ -1382,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1471,7 +1471,7 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1560,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1581,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1640,7 +1640,7 @@
         <v>4</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1726,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>6</v>
@@ -1815,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1836,7 +1836,7 @@
         <v>6</v>
       </c>
       <c r="AC13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1904,7 +1904,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1925,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1993,7 +1993,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -2082,7 +2082,7 @@
         <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
@@ -2171,7 +2171,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>6</v>
@@ -2260,7 +2260,7 @@
         <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2349,7 +2349,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2438,7 +2438,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2459,7 +2459,7 @@
         <v>8</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2527,7 +2527,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2616,7 +2616,7 @@
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2705,7 +2705,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2794,7 +2794,7 @@
         <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2883,7 +2883,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2972,7 +2972,7 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2993,7 +2993,7 @@
         <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -3061,7 +3061,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -3150,7 +3150,7 @@
         <v>6</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -3239,7 +3239,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -3328,7 +3328,7 @@
         <v>6</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3417,7 +3417,7 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3506,7 +3506,7 @@
         <v>7</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3595,7 +3595,7 @@
         <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3684,7 +3684,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3770,30 +3770,30 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>61.29</v>
+        <v>64.52</v>
       </c>
       <c r="G2">
-        <v>38.71</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3802,25 +3802,25 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>74.19</v>
+      </c>
+      <c r="G3">
+        <v>25.81</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>64.52</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>7.6</v>
-      </c>
-      <c r="I3">
-        <v>11</v>
-      </c>
-      <c r="J3">
-        <v>35.48</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4054,7 +4054,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4094,7 +4094,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4134,7 +4134,7 @@
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4154,7 +4154,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4174,7 +4174,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4214,7 +4214,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4234,7 +4234,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4254,7 +4254,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4294,7 +4294,7 @@
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4314,7 +4314,7 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4334,7 +4334,7 @@
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4902,7 +4902,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4934,22 +4934,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920075</v>
+        <v>20330051920077</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4980,22 +4980,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920077</v>
+        <v>20330051920070</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5003,45 +5003,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920077</v>
+        <v>20330051920070</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
         <v>53</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920070</v>
+        <v>20330051920075</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5049,162 +5049,70 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920070</v>
+        <v>19330051920051</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920073</v>
+        <v>20330051920059</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920051</v>
+        <v>20330051920065</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920080</v>
-      </c>
-      <c r="B10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920090</v>
-      </c>
-      <c r="B11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920059</v>
-      </c>
-      <c r="B12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920065</v>
-      </c>
-      <c r="B13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4AEV - Estadisticos 20212.xlsx
+++ b/grupos/4AEV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="149">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -212,30 +212,81 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AVENDAÑO</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>ESPINOZA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUILLEN</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
     <t>MIXCOHA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -245,30 +296,78 @@
     <t>ZGAIP</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>CASTAÑEDA</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>EVARISTO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>BAROJAS</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
   </si>
   <si>
     <t>JOAQUIN</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -278,30 +377,87 @@
     <t>OJEDA</t>
   </si>
   <si>
+    <t>AXEL JESUS</t>
+  </si>
+  <si>
     <t>MARCO ANTONIO</t>
   </si>
   <si>
     <t>PAUL ARAVIER</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>KARLA JOVANA</t>
+  </si>
+  <si>
     <t>NORKYS AIRY</t>
   </si>
   <si>
     <t>JORGE HUMBERTO</t>
   </si>
   <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
     <t>ADRIAN</t>
   </si>
   <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>DIEGO IVAN</t>
+  </si>
+  <si>
     <t>DAVID</t>
   </si>
   <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
     <t>DANIEL</t>
   </si>
   <si>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>AMANDA MICHEL</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ALDIR ADALBERTO</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
     <t>OSVALDO</t>
   </si>
   <si>
@@ -309,162 +465,6 @@
   </si>
   <si>
     <t>YAEL</t>
-  </si>
-  <si>
-    <t>AVENDAÑO</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUILLEN</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>BAROJAS</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>URBINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AXEL JESUS</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>KARLA JOVANA</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>ELIAS</t>
-  </si>
-  <si>
-    <t>DIEGO IVAN</t>
-  </si>
-  <si>
-    <t>JOHAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>AMANDA MICHEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ALDIR ADALBERTO</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1011,7 @@
         <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>8</v>
@@ -1020,7 +1020,7 @@
         <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -1058,7 +1058,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1067,7 +1067,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -1079,7 +1079,7 @@
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -1088,7 +1088,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>6</v>
@@ -1100,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>5</v>
@@ -1109,7 +1109,7 @@
         <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1121,7 +1121,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1130,7 +1130,7 @@
         <v>6</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB5">
         <v>8</v>
@@ -1168,7 +1168,7 @@
         <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -1177,7 +1177,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>5</v>
@@ -1189,7 +1189,7 @@
         <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>9</v>
@@ -1198,7 +1198,7 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1210,7 +1210,7 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1236,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -1245,7 +1245,7 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1257,7 +1257,7 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1266,7 +1266,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>5</v>
@@ -1278,7 +1278,7 @@
         <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
         <v>9</v>
@@ -1287,7 +1287,7 @@
         <v>5</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1299,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1308,7 +1308,7 @@
         <v>5</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB7">
         <v>5</v>
@@ -1367,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -1376,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>10</v>
@@ -1414,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -1423,7 +1423,7 @@
         <v>6</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1435,7 +1435,7 @@
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -1444,7 +1444,7 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>6</v>
@@ -1456,7 +1456,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -1465,7 +1465,7 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1477,7 +1477,7 @@
         <v>6</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1486,7 +1486,7 @@
         <v>6</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB9">
         <v>6</v>
@@ -1512,7 +1512,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G10">
         <v>6</v>
@@ -1533,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>5</v>
@@ -1545,7 +1545,7 @@
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1554,7 +1554,7 @@
         <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>8</v>
@@ -1566,7 +1566,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y10">
         <v>6</v>
@@ -1575,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB10">
         <v>6</v>
@@ -1610,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>5</v>
@@ -1628,13 +1628,13 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>5</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -1646,13 +1646,13 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB11">
         <v>6</v>
@@ -1678,7 +1678,7 @@
         <v>6</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G12">
         <v>6</v>
@@ -1690,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1699,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>5</v>
@@ -1711,7 +1711,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1720,7 +1720,7 @@
         <v>7</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1732,7 +1732,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1741,7 +1741,7 @@
         <v>6</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>6</v>
@@ -1779,7 +1779,7 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>6</v>
@@ -1788,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -1800,7 +1800,7 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>8</v>
@@ -1809,7 +1809,7 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1821,7 +1821,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1830,7 +1830,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>6</v>
@@ -1868,7 +1868,7 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -1889,7 +1889,7 @@
         <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>8</v>
@@ -1898,7 +1898,7 @@
         <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1919,7 +1919,7 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>7</v>
@@ -1957,7 +1957,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -1978,7 +1978,7 @@
         <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>7</v>
@@ -1987,7 +1987,7 @@
         <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1999,7 +1999,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -2055,7 +2055,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>5</v>
@@ -2067,16 +2067,16 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -2088,7 +2088,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -2097,7 +2097,7 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB16">
         <v>5</v>
@@ -2135,7 +2135,7 @@
         <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>6</v>
@@ -2144,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>6</v>
@@ -2156,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -2165,7 +2165,7 @@
         <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>7</v>
@@ -2177,7 +2177,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2186,7 +2186,7 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB17">
         <v>7</v>
@@ -2224,7 +2224,7 @@
         <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2233,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -2245,16 +2245,16 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2266,7 +2266,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -2275,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB18">
         <v>5</v>
@@ -2292,7 +2292,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -2301,7 +2301,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2313,7 +2313,7 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>6</v>
@@ -2322,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>6</v>
@@ -2334,16 +2334,16 @@
         <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2355,7 +2355,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>6</v>
@@ -2364,7 +2364,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>6</v>
@@ -2402,7 +2402,7 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>5</v>
@@ -2423,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -2432,7 +2432,7 @@
         <v>7</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2444,7 +2444,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2512,7 +2512,7 @@
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2521,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>6</v>
@@ -2533,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2568,7 +2568,7 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -2580,7 +2580,7 @@
         <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>5</v>
@@ -2589,7 +2589,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -2601,16 +2601,16 @@
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2622,7 +2622,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2631,7 +2631,7 @@
         <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB22">
         <v>5</v>
@@ -2690,7 +2690,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>6</v>
@@ -2699,7 +2699,7 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2711,7 +2711,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2720,7 +2720,7 @@
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>7</v>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>6</v>
@@ -2758,7 +2758,7 @@
         <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>6</v>
@@ -2779,7 +2779,7 @@
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2788,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2800,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2809,7 +2809,7 @@
         <v>7</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>6</v>
@@ -2847,7 +2847,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>5</v>
@@ -2868,7 +2868,7 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>8</v>
@@ -2877,7 +2877,7 @@
         <v>6</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2889,7 +2889,7 @@
         <v>6</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2898,7 +2898,7 @@
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>6</v>
@@ -2957,7 +2957,7 @@
         <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>8</v>
@@ -2966,7 +2966,7 @@
         <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>10</v>
@@ -3025,7 +3025,7 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>7</v>
@@ -3046,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>7</v>
@@ -3055,7 +3055,7 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -3114,7 +3114,7 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -3123,7 +3123,7 @@
         <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>6</v>
@@ -3135,7 +3135,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>7</v>
@@ -3144,7 +3144,7 @@
         <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -3156,7 +3156,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -3165,7 +3165,7 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -3203,7 +3203,7 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
         <v>5</v>
@@ -3212,7 +3212,7 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>6</v>
@@ -3224,7 +3224,7 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -3233,7 +3233,7 @@
         <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>7</v>
@@ -3245,7 +3245,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3292,7 +3292,7 @@
         <v>5</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -3313,7 +3313,7 @@
         <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>9</v>
@@ -3322,7 +3322,7 @@
         <v>6</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>6</v>
@@ -3381,7 +3381,7 @@
         <v>8</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>6</v>
@@ -3402,7 +3402,7 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -3423,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3432,7 +3432,7 @@
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>8</v>
@@ -3449,7 +3449,7 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -3458,7 +3458,7 @@
         <v>6</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G32">
         <v>6</v>
@@ -3470,7 +3470,7 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>5</v>
@@ -3479,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>5</v>
@@ -3491,16 +3491,16 @@
         <v>6</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>7</v>
@@ -3512,16 +3512,16 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y32">
         <v>6</v>
       </c>
       <c r="Z32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB32">
         <v>6</v>
@@ -3547,7 +3547,7 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>7</v>
@@ -3568,7 +3568,7 @@
         <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>6</v>
@@ -3580,7 +3580,7 @@
         <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>5</v>
@@ -3589,7 +3589,7 @@
         <v>5</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
         <v>6</v>
@@ -3601,7 +3601,7 @@
         <v>7</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3610,7 +3610,7 @@
         <v>6</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB33">
         <v>6</v>
@@ -3636,7 +3636,7 @@
         <v>7</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -3657,7 +3657,7 @@
         <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>8</v>
@@ -3669,16 +3669,16 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -3699,7 +3699,7 @@
         <v>6</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>6</v>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3770,30 +3770,30 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>74.19</v>
+      </c>
+      <c r="G2">
+        <v>25.81</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>64.52</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>7.6</v>
-      </c>
-      <c r="I2">
-        <v>11</v>
-      </c>
-      <c r="J2">
-        <v>35.48</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3802,19 +3802,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>74.19</v>
+        <v>77.42</v>
       </c>
       <c r="G3">
-        <v>25.81</v>
+        <v>22.58</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3834,19 +3834,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>77.42</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="G4">
-        <v>22.58</v>
+        <v>19.35</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3878,7 +3878,7 @@
         <v>19.35</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3910,7 +3910,7 @@
         <v>16.67</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3930,25 +3930,25 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="G7">
+        <v>12.9</v>
+      </c>
+      <c r="H7">
+        <v>7.1</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>83.87</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>7</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>16.13</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3990,7 +3990,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4015,326 +4015,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920071</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920071</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920072</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920072</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920074</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920074</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920075</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920077</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920089</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920089</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920092</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920059</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920070</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920070</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920069</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920386</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4370,200 +4050,200 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920071</v>
+        <v>20330051920041</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920072</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920074</v>
+        <v>20330051920072</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920089</v>
+        <v>20330051920073</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920070</v>
+        <v>20330051920359</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920075</v>
+        <v>20330051920074</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920077</v>
+        <v>20330051920075</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920092</v>
+        <v>19330051920051</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920059</v>
+        <v>20330051920077</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920069</v>
+        <v>20330051920080</v>
       </c>
       <c r="B11" t="s">
         <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920386</v>
+        <v>20330051920081</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920041</v>
+        <v>20330051920082</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
         <v>130</v>
@@ -4574,13 +4254,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920073</v>
+        <v>20330051920084</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
         <v>131</v>
@@ -4591,13 +4271,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920359</v>
+        <v>20330051920087</v>
       </c>
       <c r="B15" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
         <v>132</v>
@@ -4608,13 +4288,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920051</v>
+        <v>20330051920088</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
         <v>133</v>
@@ -4625,13 +4305,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920080</v>
+        <v>20330051920089</v>
       </c>
       <c r="B17" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
         <v>134</v>
@@ -4642,13 +4322,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920081</v>
+        <v>20330051920090</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
         <v>135</v>
@@ -4659,16 +4339,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920082</v>
+        <v>20330051920091</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4676,16 +4356,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920084</v>
+        <v>20330051920092</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4693,16 +4373,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920087</v>
+        <v>20330051920093</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4710,16 +4390,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920088</v>
+        <v>20330051920059</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4727,16 +4407,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920090</v>
+        <v>20330051920061</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4744,16 +4424,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920091</v>
+        <v>20330051920062</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4761,13 +4441,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920093</v>
+        <v>20330051920063</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>141</v>
@@ -4778,13 +4458,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920061</v>
+        <v>20330051920064</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D26" t="s">
         <v>142</v>
@@ -4795,13 +4475,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920062</v>
+        <v>20330051920065</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D27" t="s">
         <v>143</v>
@@ -4812,13 +4492,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920063</v>
+        <v>20330051920066</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D28" t="s">
         <v>144</v>
@@ -4829,13 +4509,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920064</v>
+        <v>20330051920068</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
         <v>145</v>
@@ -4846,13 +4526,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920065</v>
+        <v>20330051920070</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>146</v>
@@ -4863,13 +4543,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920066</v>
+        <v>20330051920069</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>147</v>
@@ -4880,13 +4560,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920068</v>
+        <v>20330051920386</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
         <v>148</v>
@@ -4902,7 +4582,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4934,45 +4614,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920077</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920077</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4983,13 +4663,13 @@
         <v>20330051920070</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -4998,7 +4678,7 @@
         <v>58</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5006,65 +4686,65 @@
         <v>20330051920070</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920075</v>
+        <v>20330051920069</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920051</v>
+        <v>20330051920069</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5072,47 +4752,139 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920059</v>
+        <v>20330051920386</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>20330051920386</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920074</v>
+      </c>
+      <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920051</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
+        <v>126</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920077</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
         <v>20330051920065</v>
       </c>
-      <c r="B9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9">
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>
